--- a/Xlsx filer/365Discount_produkter.xlsx
+++ b/Xlsx filer/365Discount_produkter.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:L115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -507,41 +507,41 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Taffel chips*</t>
+          <t>K-Salat pålægssalat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Taffel</t>
+          <t>K-Salat</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>. 160-175 g</t>
+          <t>. 100-150 g</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75,00. kr/kg</t>
+          <t>100,00. kr/kg</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1030003</t>
+          <t>1034755</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3ca891306a17616fa95d89f89e6c2073&amp;w=552&amp;s=f4f1932136f180f7c4625ff83615a361</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbc56740eb8d4466069b508165fc877d7%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F11107e90e3db9b25d4d8e41ab6b8a0da%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fab847c2833c1918b903e8a40f9a736eb&amp;w=552&amp;s=ff5390597dcef4a373de4d2ab32bfca2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9bcc313966cc64cd</t>
+          <t>fc1303ec5692af0e</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -559,41 +559,41 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ribena*</t>
+          <t>Magnum is*</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ribena*</t>
+          <t>Magnum</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>85 cl</t>
+          <t>. 255-330 ml</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23,53. kr/l</t>
+          <t>94,12. kr/l</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1029980</t>
+          <t>1034752</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb0d6febcc0ba22190cb11d3847402f53&amp;w=252&amp;s=696cabba8db553002cf5698f123943c0</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fcf6bccb0406d7f210e89296e1116bafa&amp;w=252&amp;s=59a184d964e0de7d0712270e80ec4bc0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>94c46b3e85c16b3e</t>
+          <t>81837e787a46a5d9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -611,41 +611,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Coop yoghurt</t>
+          <t>Rød peber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Rød</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>. 1 kg</t>
+          <t>. Stk</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10,00. kr/kg</t>
+          <t>6,00. kr/stk</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1029978</t>
+          <t>1034879</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fce77adbb9ebd3247da98a34affb6ffbd%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1b86b678579baf0a7432ca013fb07dea%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F69f400b471e52cadbd0e0b881f3c6f47&amp;w=252&amp;s=54c61145e18937903ebc4f1c5427c14d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff4f26920b405ae8245c6e2cb43b349bb&amp;w=552&amp;s=9b6fb29a42c62edf6eed4778f2f460c7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bc49575659d841e9</t>
+          <t>c74c6c3c34da3a93</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -663,41 +663,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Coop kartofler</t>
+          <t>Hakket kylling 7-10%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Hakket</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>. 450-1000 g</t>
+          <t>1000 g</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22,22. kr/kg</t>
+          <t>45,00. kr/kg</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1029979</t>
+          <t>1034881</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9513dedaf85f2d340fa9a6ba7572be9d&amp;w=417&amp;s=ca76ebd078e2d51ae38d5051ea74539d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff28d7d9d01a0e4b2405a2546783cd875&amp;w=552&amp;s=a06578556e71a9b0431edf2cbb3d2ddb</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>804252dc3faf2dad</t>
+          <t>9533c799cec431cc</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -705,7 +705,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1000 g</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -715,41 +719,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Coop Asia cubes</t>
+          <t>Capri-Sun*</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Capri-Sun*</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>. 350 g</t>
+          <t>. 10 x 20 cl</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>51,43. kr/kg</t>
+          <t>10,00. kr/l</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1030097</t>
+          <t>1034882</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd47d4693b30b7e49bae48949351970b7&amp;w=552&amp;s=78714bb7f12c9246b716b846049f6e4e</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4a08f9cbaae5c886af64ac41c551b99b%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff1b440bedc249996de2221c82abdfb60%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9aa954c8eee819cbfacbf8572f87943b&amp;w=252&amp;s=062ffbaea09ffc5de93c122ed15364c8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9e964c4e866379b2</t>
+          <t>907a580b0ff578bc</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -767,41 +771,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mørbrad af gris</t>
+          <t>Cheasy yoghurt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mørbrad</t>
+          <t>Cheasy</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1650-2300 g</t>
+          <t>1 kg</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60,00. kr/kg</t>
+          <t>10,00. kr/kg</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1030098</t>
+          <t>1034757</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F956766adcecdb33d1aac76094d825f29&amp;w=252&amp;s=3bb4411b88bddcab61c2a0656f5eef31</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3abd256bb1135bac04b28dd288539d33&amp;w=252&amp;s=4c3d5a411f634c5c545e2ff960b87b73</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>80d77f282a57c59c</t>
+          <t>a0d01f2f7eca6a2c</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -819,41 +823,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Spier Signature</t>
+          <t>Kims chips*</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spier</t>
+          <t>Kims</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>. 75 cl</t>
+          <t>. 75-95 g</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>46,67. kr/l</t>
+          <t>133,33. kr/kg</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1030096</t>
+          <t>1034758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2625308dca006800860897b039defdc0&amp;w=252&amp;s=c61f852db4d386b6cd9d1cc892bb23cb</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=612&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4f9ea6225e9e0333fa389283b4aa0048&amp;w=552&amp;s=797c95dc904ad4eee6301af9c5b2b5e7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>c13f6a9436c936c9</t>
+          <t>e5b73ee162c80c72</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -871,41 +875,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Danske Egnsgårde flæskesteg</t>
+          <t>Cheasy hytteost</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Danske</t>
+          <t>Cheasy</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>250 g</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>70,00. kr/kg</t>
+          <t>40,00. kr/kg</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1029987</t>
+          <t>1034756</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd518042de62c83ed791956af101b636f&amp;w=552&amp;s=933817c4c86ad86d4c9772053f71c423</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F37ada5ab0761a82634016cd2a9524b86&amp;w=552&amp;s=1d1efce31ed7a4444cbe5575f3739dab</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bf866019146f1377</t>
+          <t>93b43a338e1c8ece</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -923,41 +927,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Danske Egnsgårde marineret kalvesteak</t>
+          <t>Sun Lolly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Danske</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>125 g</t>
+          <t>. 8 x 60 ml</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>160,00. kr/kg</t>
+          <t>29,17. kr/l</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1029982</t>
+          <t>1034760</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa1677ecb7083929e1134d98e8745cd44&amp;w=252&amp;s=9dca3afa53eb569d2e3804cf8a64503b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5f9c3d27e7347df3b966e8b09b45de00&amp;w=252&amp;s=f71750aeba5175fe9b0d398ae6226c34</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>b36a48953771e84e</t>
+          <t>8570362ec1d93db3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -975,41 +979,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Coop marineret lammekrone af nakke</t>
+          <t>Gøl pølser*</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Gøl</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>275-400 g</t>
+          <t>339-420 g</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>287,27. kr/kg</t>
+          <t>85,55. kr/kg</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1029983</t>
+          <t>1034759</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6990198b49cbb32a54d6cf3219891349&amp;w=252&amp;s=83334304875723197cb23a0910800767</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0fb8165e43b965e3eb1c816ab8b4be16&amp;w=302&amp;s=4dda9246ca6ecb4cb38dbe5759df8e29</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>be83407a63ac3e93</t>
+          <t>93cd3cb61e916a68</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1027,7 +1031,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Coop koteletter</t>
+          <t>Coop paneret kylling</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1037,31 +1041,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>500 g</t>
+          <t>. 200-250 g</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>70,00. kr/kg</t>
+          <t>60,00. kr/kg</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1029986</t>
+          <t>1034762</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbc822583d3f5fd5a5d0b99c816d48767&amp;w=552&amp;s=c45a8b6045c09174ed58e7f7e810b822</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=612&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F73ace2b214724147207c58382cdc4c2a%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2c79a44550caa29c0e995844b2f60bd2&amp;w=552&amp;s=5c24a03c85c259ee6dc2a011252c7767</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ea4815b76b6ab6c0</t>
+          <t>917c65c3fed43103</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1079,41 +1083,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Coop marineret chuck eye steak</t>
+          <t>Oreo*</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Oreo*</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>275-375 g</t>
+          <t>154-157 g</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>236,36. kr/kg</t>
+          <t>77,92. kr/kg</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1029985</t>
+          <t>1034763</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb4feccfc6ae9007ea1b44b1791ea51ce&amp;w=552&amp;s=70f5a960ff5ac85e6824ab93b7982282</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1d4bee6d0854cc9fbaf1ff129b3e765b&amp;w=252&amp;s=d1b9710425e4ae45955ea321ccd1d28d</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>c7399866719a3669</t>
+          <t>d5b67f427a920b28</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1131,41 +1135,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Coop stegeflæsk</t>
+          <t>Haribo slikpose*</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Haribo</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>. 120 g</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>72,50. kr/kg</t>
+          <t>100,00. kr/kg</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1059744</t>
+          <t>1034764</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F54a0e5a0f6291272ea5c310ab807debf&amp;w=552&amp;s=95aff4cfc562b41a2db246a72046e779</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb7e08be0c2ee7405733e2aeae96ff5fb&amp;w=227&amp;s=798280b7ab190580d963f65bbbdbbeff</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>c1699696cb928f4b</t>
+          <t>93c8b1a1174fb8ec</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1183,41 +1187,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Frijsenborg hel kylling</t>
+          <t>Coop hakket oksekød 14-18%</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Frijsenborg</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1350 g</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>51,11. kr/kg</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>69</v>
-      </c>
+          <t>94,88. kr/kg</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1029989</t>
+          <t>1034770</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa4857fdd2d8d812a7824c9f085ed790e&amp;w=169&amp;s=db2fcfb4c4db1d5e0998c459c5041bba</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F68d27b6752224a330f520bf15e8c96cd&amp;w=552&amp;s=282a880255a6bccef3ee3d86fe4ceb3b</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8791479c788727c7</t>
+          <t>c33834cf66cc6533</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1235,39 +1237,41 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hele kyllingelår</t>
+          <t>Coop medister</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hele</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2000 g</t>
+          <t>500 g</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>34,50. kr/kg</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>48,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>24</v>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1053785</t>
+          <t>1034767</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F75b0389d98a8e86dcb98b7b3e57e0255&amp;w=1152&amp;s=0d87ec723db7afe9047b9e4f3ac7ea23</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F86b64aa7103126d94c644b20d3e333e9&amp;w=552&amp;s=67b12b42c1b5e61346304901cc799760</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>996636396399cc33</t>
+          <t>c7649a934c9a6d6c</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1285,7 +1289,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Coop Conference pærer</t>
+          <t>Coop nakkefilet</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1295,31 +1299,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>. 1 kg</t>
+          <t>1100 g</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16,00. kr/kg</t>
+          <t>71,82. kr/kg</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1029993</t>
+          <t>1034774</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffc884a98dea0dc4913b2eecb48e6c4b0&amp;w=552&amp;s=db056bd251e98dfc62d58882503aa739</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fce0c16a9ccd38c85bf332fae872dc6de&amp;w=252&amp;s=14a5b2b4dbca27fcfb2f1f698cd7b590</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>ce3c31d3698e306d</t>
+          <t>d0364b9d6a383b33</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1337,41 +1341,41 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Coop røde kernefri druer</t>
+          <t>Jensens Køkken sauce*</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Jensens</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>. 500 g</t>
+          <t>250-350 ml</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>40,00. kr/kg</t>
+          <t>64,00. kr/l</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1043924</t>
+          <t>1034766</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F61b29140042a2e58665f713d6dd79804&amp;w=202&amp;s=2b27ff3fcc1dd82bade969f757774868</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa42f5f4cddb7a5b0b7f4a36cc0310424%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc9888fae13143e2e1659c04849666f4e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fabe5805063ea864a9be2b607288c7fcb%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffce21d15c7c1218cab8c5208a999d1ea&amp;w=252&amp;s=fb39717525de433eba634520448c5f57</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>af3891f361c7508d</t>
+          <t>da5e4e392025bf29</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1389,7 +1393,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Coop hindbær</t>
+          <t>Coop marineret flanksteak med oregano og hvidløg</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1399,31 +1403,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>. 125 g</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>120,00. kr/kg</t>
+          <t>220,00. kr/kg</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1029994</t>
+          <t>1034768</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2e4bd322a47537113e8263cd7438198c&amp;w=252&amp;s=4c6c73690c0dd21990ae89751ba8f59a</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdb575c8a9c5b9cbb4df00c436965d35f&amp;w=252&amp;s=1e6a0991c66c8dd5ce4cb818e49312fc</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>af5b803542d87f2a</t>
+          <t>eada01351ff0744b</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1441,41 +1445,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Änglamark økologisk dansk agurk</t>
+          <t>Hele kyllingelår</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Hele</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>. Stk</t>
+          <t>2000 g</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10,00. kr/stk</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
+          <t>34,50. kr/kg</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1029992</t>
+          <t>1054380</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4c002e1d1db39e5a790a1584298b15ab&amp;w=252&amp;s=5b2fb107d7f8e5abd8218475fdd1a8d6</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F70d4c5923fe81116834fdc7090c29883&amp;w=1152&amp;s=165b3e82de12b47e897ea7f98f2b17c8</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>cc9931666c9933b3</t>
+          <t>996636396399cc33</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1493,41 +1495,41 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Honningmelon</t>
+          <t>Langelænder pølser*</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Honningmelon</t>
+          <t>Langelænder</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>. Stk</t>
+          <t>1400-1500 g</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18,00. kr/stk</t>
+          <t>63,57. kr/kg</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1029995</t>
+          <t>1034778</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff95646694cf33f1f7aa2c3bd9b0cfed6&amp;w=252&amp;s=ffff3c90040552b220ec5dff65686d57</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff632f5dfc3f4f74b2a16f1fbb17cd7c7%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F29293cdb14dddf70c5d42c8ca76542a1%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe3ec527568134be7f0aa6bbc5295cd33&amp;w=552&amp;s=594d36916f04d1ac7404d1698b9da8b6</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>c0c02f2f3f35f4d0</t>
+          <t>df4920b60e27d359</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1545,41 +1547,41 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dansk Nordic crisp salat fra Katrine &amp; Alfred</t>
+          <t>Coop feta*</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dansk</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>. 75 g</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>186,67. kr/kg</t>
+          <t>120,00. kr/kg</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1030026</t>
+          <t>1034776</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0cfe15ef96cb74bf8be0c35ca0049d2f&amp;w=252&amp;s=4782a4c041b19174289c94a6572f0a0c</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1631bb3d477c0a26b19630fdba66d001&amp;w=266&amp;s=d57ebff16390630f7b59bdf14d0b1573</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>c087b4336d687e6c</t>
+          <t>820f3dda703535ab</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1597,41 +1599,41 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Courget</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Courget</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>200 g</t>
+          <t>. Stk</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>60,00. kr/kg</t>
+          <t>6,00. kr/stk</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1030001</t>
+          <t>1034781</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6f4728246dc0ceaeeef7048fe336a134&amp;w=552&amp;s=207baadc12a739481ae016aac97154e5</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9a20dd71fa9720adf8fa2389d9a028c7&amp;w=252&amp;s=e9b076d251662a7c61ef1234090348a5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>c78e6d4c366592b2</t>
+          <t>a5bf5240abbf1541</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1649,41 +1651,41 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kolios græsk yoghurt*</t>
+          <t>Heinz ketchup*</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kolios</t>
+          <t>Heinz</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1 kg</t>
+          <t>570 g</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>25,00. kr/kg</t>
+          <t>31,58. kr/kg</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1030104</t>
+          <t>1034779</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff0763d29e0dda6a89aa94658ce1a7680%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fcc271f8c68c1dc46bd17b1357f1eb657&amp;w=252&amp;s=1eac0646d0e15af15e204339b0fe706e</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Feb4e3ba7546b85d7dd58d4651e8aa540&amp;w=252&amp;s=f810dc27e66c683b693b5573a555d15d</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>91ec7f456a332233</t>
+          <t>cd39cccc3399634c</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1701,41 +1703,41 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mentos*</t>
+          <t>Graasten kartoffelsalat*</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mentos*</t>
+          <t>Graasten</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>38 g</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>131,58. kr/kg</t>
+          <t>50,00. kr/kg</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1043925</t>
+          <t>1034777</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdf610eb59c03c9ce576448a50c6ee6e8&amp;w=252&amp;s=36c77faf3ad4e62e7f8efd64aafe34a0</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa853f748eee0cd59921a8f4b5466dfdd%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0b756c550e7b3b51470e103555613d98&amp;w=252&amp;s=5a7adc542d5cdc7cde602f87a2f10d60</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>94216bd736358d6a</t>
+          <t>9c6c7290eb959c66</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1753,22 +1755,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Xtra! Ispinde*</t>
+          <t>Salat, skyllet og klar til brug</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Xtra!</t>
+          <t>Salat,</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>. 300 ml</t>
+          <t>75 g</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>33,33. kr/l</t>
+          <t>133,33. kr/kg</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1777,17 +1779,17 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1030004</t>
+          <t>1034780</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6881672237392a78f7b7c6bb77cd61e9%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0e640cb608773982c33f3ee452bb386a&amp;w=252&amp;s=4ff717604b1412c991e26183b8eb3fd4</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fda81ed2a56f5204074b2a971627e304b&amp;w=252&amp;s=44e15cbdc3d402bd106055a8a9de0a89</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>ddee623942869363</t>
+          <t>9b52642d65d38b78</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1805,41 +1807,33 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Coop kylling</t>
+          <t>Änglamark økologiske bananer</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Coop</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>. 750-1500 g</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>46,67. kr/kg</t>
-        </is>
-      </c>
+          <t>Änglamark</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1030007</t>
+          <t>1034783</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fea730fa7c606c421f8a8de5a31309052&amp;w=252&amp;s=4b7691f763561ec3adb41a1cb8adfb89</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9470a954e7071e9384ee9336745e0aef&amp;w=552&amp;s=eba33f6415b0299d6661686196888e6b</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>8699596629e9a6b6</t>
+          <t>9473722e4b8969b5</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1857,41 +1851,41 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Coop færdigret</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>. 350 g</t>
+          <t>. Stk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>51,43. kr/kg</t>
+          <t>10,00. kr/stk</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1030010</t>
+          <t>1034784</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6fedac7552735296c06b3ac502e4b823%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd71ed3692f7ac0072e70e4b56bafdf60%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1ff28ca7d588ccfcb7d663f279ca9a61&amp;w=252&amp;s=d4430110c1e3da421c6fe08df3373053</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F48b9ceb46bae7e33ea968eebadd07acc&amp;w=552&amp;s=7bcf12db1501ea9352112357e0026345</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>cfe304573909745e</t>
+          <t>9a9849696d733533</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1909,41 +1903,41 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Stay Strong skyr*</t>
+          <t>Galiamelon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Stay</t>
+          <t>Galiamelon</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>500 g</t>
+          <t>. Stk</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>32,00. kr/kg</t>
+          <t>20,00. kr/stk</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1030012</t>
+          <t>1034786</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1b83b300115fe0fc173ef57a9d38edd0&amp;w=552&amp;s=6d27257aca7da66998a559b938fd0dea</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F425ae8e87f14ed5299faf279264cbe1c&amp;w=252&amp;s=e7556ac2a594122320f70828db04489b</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>c1836afc3f24276c</t>
+          <t>958356cd6a0e6a3e</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1961,22 +1955,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kærgården smørbar</t>
+          <t>Formodne avocadoer</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kærgården</t>
+          <t>Formodne</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>200 g</t>
+          <t>. 3 stk</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>90,00. kr/kg</t>
+          <t>6,00. kr/stk</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1985,17 +1979,17 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1030014</t>
+          <t>1034787</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F331c5dbfa3587a30455f9ece1e4d0055%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc7fbedff0b74491f28e049ff1536ae24&amp;w=552&amp;s=771935b2cb29064649d77432d91f9d8e</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7a56aa49f5d8aa140550a61ff3db4a36&amp;w=252&amp;s=2d678dc0fb3caf59015a1fe622b5207f</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>9966546e6e6a9998</t>
+          <t>939c96e69ac99c8a</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2003,7 +1997,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>3 stk. pr.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2013,41 +2011,41 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Matilde kakao skummetmælk</t>
+          <t>Irma blåbær</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Matilde</t>
+          <t>Irma</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1 l</t>
+          <t>. 200 g</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>14,00. kr/l</t>
+          <t>160,00. kr/kg</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1043926</t>
+          <t>1048626</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa88d9c58a0d57d73208edfda96069bec&amp;w=252&amp;s=b8d613c47e6f1d39d0538ea1d360c4ff</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F49f214345531ed36643e7b3bdf4522c5&amp;w=385&amp;s=59c59635ab89a5922ba0046cae6214cf</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>9a6c319b669a9333</t>
+          <t>d7180a3fd0e3423f</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2065,41 +2063,41 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Coop dansk piskefløde</t>
+          <t>Aalbæk spegepølse i skiver</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Aalbæk</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>500 ml</t>
+          <t>60 g</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>40,00. kr/l</t>
+          <t>266,67. kr/kg</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1030016</t>
+          <t>1034791</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffbb6db4adadcb2a865463bcf291c4ce8&amp;w=252&amp;s=dd055f1eff3e83a07f07d4b5c5ba98ee</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa349eb2605ee926eeefcda315387cf5b&amp;w=252&amp;s=b78352d25f74c098091b5ee6ff97c3eb</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>c3cf9e9898c6938c</t>
+          <t>db0c64323aca6be3</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2117,41 +2115,41 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Valsølille juice*</t>
+          <t>Kohberg hvedebrød</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Valsølille</t>
+          <t>Kohberg</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>850 ml</t>
+          <t>. 380-500 g</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>29,41 kr/l</t>
+          <t>47,37. kr/kg</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1030101</t>
+          <t>1034792</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6ac2e8445079f780d1453a04cd2e82a0%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2a2eb3c9593f81dc206a1eca53da50ad%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F273159940910c4f234fb74c3777d6005&amp;w=552&amp;s=757643b2c4d5d1acc84c41a299a3058d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F61f165afb25f96bca795b4eb565a21b5%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F59b6625d45ec457bbe40c16fbd1e1515%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F16b7c76c88204a13873a2802b58451bf&amp;w=252&amp;s=3e8269d2fd3b5389bccf12aec636a625</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>923d69cd6d983296</t>
+          <t>95701aaf7f8a2c1c</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2169,41 +2167,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Coop iskaffe*</t>
+          <t>Tulip bacon 3-pak</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Tulip</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>250 ml</t>
+          <t>3 x 125 g</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>24,00. kr/l</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>6</v>
-      </c>
+          <t>93,20. kr/kg</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1043932</t>
+          <t>1034793</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8aa14a6ec819d87f6f7bcf06ac2dea6c%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F15eee84c1534b7df3ccbb70ff4cd5b32&amp;w=243&amp;s=e271fd338092101756659e9e4b2c2b10</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F75b95e65a141d19fcdc8214b35ce1c38&amp;w=252&amp;s=070824199a471d1ebe080f8bd9f19148</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>e6512424496b5b7f</t>
+          <t>a76658991962b69d</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2221,17 +2217,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pågen sanwichbrød*</t>
+          <t>Stryhns leverpostej*</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pågen</t>
+          <t>Stryhns</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>400-900 g</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2245,17 +2241,17 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1030109</t>
+          <t>1034790</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F70cc6c924bae52ce3e5225020de6fb92&amp;w=552&amp;s=adc50bb4a6a831fccf8625e2d4c1d34d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff8c35430559f4260c1952eb74aa237dd%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fcbe2e3d822215ecfd7e82285a8bec5d6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F494b93f91e0066315bf3e863ea7cc049&amp;w=252&amp;s=3cf177ac48dd630654fe2cf99013401e</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>c88f37509fb0e80f</t>
+          <t>d1f7d58a207aeaa0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2273,22 +2269,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pålækker pålægssalat*</t>
+          <t>Amanda gulfinnet tun*</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pålækker</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>105 g</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>80,00. kr/kg</t>
+          <t>114,29. kr/kg</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2297,17 +2293,17 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1030106</t>
+          <t>1034795</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd1a95d211a8001e33ec9f417df6bf324&amp;w=252&amp;s=9cdf98776f520e10d4f1b46119fd5fc0</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F42d8e8d3f06ef567b299df8126a250be%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa81e23b12d6f78c8737bafbcf8b3818c&amp;w=552&amp;s=d37e89718f195457a143be1e9a0cf206</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>c0be6f4032cb1db5</t>
+          <t>80975739627e7938</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2325,41 +2321,41 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Gårdlykke hel spegepølse*</t>
+          <t>Royal Greenland Diskobay kutterrejer</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Gårdlykke</t>
+          <t>Royal</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>220 g</t>
+          <t>230 g</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>113,64. kr/kg</t>
+          <t>195,65. kr/kg</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1030019</t>
+          <t>1048628</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2b887b3aa6146856106900354bf049aa%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2ea56c0c577618353e8b54d0c24c94c5%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F88211795a06afde94a04e3f0108e3c78&amp;w=252&amp;s=073ea9eea9a87338d5992e0c1aa0e9b1</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdf0ab0b622487d13c15db283840ad55c&amp;w=252&amp;s=711016fd5698a5c51367fbcc65279e65</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>d4f7750822296f35</t>
+          <t>c14c16971e7b6b4c</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2377,41 +2373,41 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Frokost favorit pålæg*</t>
+          <t>Glyngøre kullerfilet</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Frokost</t>
+          <t>Glyngøre</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>80-100 g</t>
+          <t>225 g</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>142,86. kr/kg</t>
+          <t>173,33. kr/kg</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1030020</t>
+          <t>1034798</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F10dbb82af7b4c85c33f18df7389d6839&amp;w=552&amp;s=878a86f52bb9b43a4b0cdcfc46692b59</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0ec9d9a900838a72df69ef6eacfea760&amp;w=252&amp;s=afc7d443861039b8f6640b762f496b11</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>c0bf631c6fb16390</t>
+          <t>c41f2ee43113973b</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2429,41 +2425,41 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Thise økologisk skiveost</t>
+          <t>Glyngøre lakseportioner</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thise</t>
+          <t>Glyngøre</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>225 g</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>100,00. kr/kg</t>
+          <t>191,11. kr/kg</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1030021</t>
+          <t>1034794</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb9365626dc7cb9bf0dae7b82635afc26%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2995d5e390106862a1518af374ae32e1&amp;w=552&amp;s=b976ffaed1484f06c398b4c2a7988910</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa0c58b46fbce52b47359e1e0d7f8be5e&amp;w=418&amp;s=439e14f261c6dc86b22928fad4d81ad1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>913f7ac2c6c5e5c0</t>
+          <t>c03b6cdf103bd4cc</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2481,41 +2477,41 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Valsemøllen melblanding*</t>
+          <t>Polar is</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Valsemøllen</t>
+          <t>Polar</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1000 g</t>
+          <t>. 1 l</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>10,00. kr/kg</t>
+          <t>20,00. kr/kg</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1030023</t>
+          <t>1034804</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa5da7331e2be1025a760ce7cd2593dae&amp;w=552&amp;s=d8a5b692d6722407465c70f010c2185f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fee3917f0d07d64d3df9dab6f111f80c7%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdb54330ce073edcacd43d64a718ed9dd&amp;w=552&amp;s=4db1fabe17ba954a9d79d23b6d198d18</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>9bc9399c39983996</t>
+          <t>90d76f282f4b1f22</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2533,41 +2529,41 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cheasy fraiche</t>
+          <t>Spangsberg is</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cheasy</t>
+          <t>Spangsberg</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>500 g</t>
+          <t>. 360-450 ml</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>28,00. kr/kg</t>
+          <t>80,56. kr/l</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1030015</t>
+          <t>1034803</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe2f05e498d599e70b624251af1ce2e4b&amp;w=226&amp;s=4a04d60d3b31dba9eef4791f997c0339</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe347bd087aa51590bc7e4b878a42a6fe&amp;w=552&amp;s=5543c91b3a75ef7b5845e510c453aed5</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>95ecebce1e374041</t>
+          <t>c76c39cb3c98e131</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2585,41 +2581,41 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Änglamark økologisk fettucine</t>
+          <t>Starbucks proteiniskaffe*</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>250 g</t>
+          <t>330 ml</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>48,00. kr/kg</t>
+          <t>45,45. kr/l</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1043927</t>
+          <t>1034807</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2901372cdcae4475761eb5f323ebbbb8&amp;w=252&amp;s=76aeeea708a22d85775a939d35c8bd6c</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fed84c2cc76603758507bd8d990f63cca%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd4716187af4a7d41a7c912604bde9fe2&amp;w=552&amp;s=8fedbcf570337ca91ff3a8aa5ff6a153</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>c4926e6d3cca3dc1</t>
+          <t>a25555714d0e7aba</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2637,41 +2633,41 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Det Gode fra Schulstad*</t>
+          <t>Pandekager med hytteost*</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Det</t>
+          <t>Pandekager</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>. 360-950 g</t>
+          <t>200-240 g</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>50,00. kr/kg</t>
+          <t>100,00. kr/kg</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1030024</t>
+          <t>1034805</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F29fb2a565fce2c7b5a86e6cccf3b2a46&amp;w=252&amp;s=7a7be36acc66cb9dec4fd51b5d61b376</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F058c1339aa5e59b7dde5a19d50578970%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8d9f3caf6d26a3f0d66593621bc543b2&amp;w=252&amp;s=b30ea1c6aa2ca9cb1d9530501e5cfffe</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>c900757d7a7a32ca</t>
+          <t>d8e70d9977361216</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2689,41 +2685,41 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Änglamark økologiske boller</t>
+          <t>LinusPro Whey100 proteinpulver*</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>LinusPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>. 420 g</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>35,71. kr/kg</t>
+          <t>222,50. kr/kg</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1030022</t>
+          <t>1048629</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F38a795f73109bdb060d6edc8d415f39e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff52dbccb8fbd9cd345a2c3497e93e97d&amp;w=252&amp;s=0fa74c8415772641860a134ac5fe628f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7c9e2b776407a5350b9ea4160d71adcc%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F409ee3743ca8ffcac5890176d6712504%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd362c960c4e339ec00c8a1aa16b73dbb&amp;w=252&amp;s=699a236247c2e4101cdca1e637b114e7</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>c9c24c4d55e96d93</t>
+          <t>b5b31a484c5de5aa</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2741,41 +2737,41 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Steff Houlberg leverpostej*</t>
+          <t>Thise økologisk græsk inspireret yoghurt</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Steff</t>
+          <t>Thise</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>450 g</t>
+          <t>1 kg</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>33,33. kr/kg</t>
+          <t>28,00. kr/kg</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1030030</t>
+          <t>1034814</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6aabf436da8397d3c41fc06a82c280d0&amp;w=552&amp;s=99b699da134558aefa320e0e7ca0c66b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7d284ea778cc1b0ccdc74263379c75c2&amp;w=552&amp;s=2c5fb43d317a52fda5a4a926101b9dd5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>8ec91937cbcc3934</t>
+          <t>cf993c1983c7c919</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2793,41 +2789,41 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Coop dressing*</t>
+          <t>Thise økologisk skiveost</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Thise</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>. 270 g</t>
+          <t>. 180-200 g</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>44,44. kr/kg</t>
+          <t>144,44. kr/kg</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1030028</t>
+          <t>1034810</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3c2bbee5dae87bda6b7dbfdc206b4fcf%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F25f673d611efd2a43f15ebd7724331e9%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8b8ef34db0bcafc91af850a3bc1b445d%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0f89a29428814237bf0b8b12b8ac6426&amp;w=552&amp;s=a50f0b779c0849f407da492dec38cb79</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F680edf422655ac074e41e8612c3d2007&amp;w=552&amp;s=7fb3269a6ec06432dad5612284245ca3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>95693f9ee0629163</t>
+          <t>d7620cb431772ab3</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2845,41 +2841,41 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Coop snackpeber</t>
+          <t>Thise økologisk skæreost</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Thise</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>. 500 g</t>
+          <t>. 432 g</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>32,00. kr/kg</t>
+          <t>113,43. kr/kg</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1029996</t>
+          <t>1034815</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd2434bedb6ec9bea43d301b9b844aa96&amp;w=552&amp;s=37398ee38ad6cb117ce43ac039a066fd</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fecbeed87751716d17eeb7ba2d1fc8672&amp;w=252&amp;s=a194f2d3177aaffb917245f7ac4a287c</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>cf386561b62c31ce</t>
+          <t>d7e32a952d1d6a0a</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2897,41 +2893,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Coop kartoffelsalat*</t>
+          <t>Thise økologisk piskefløde</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Thise</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>800 g</t>
+          <t>500 ml</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>35,00. kr/kg</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>28</v>
-      </c>
+          <t>49,90. kr/l</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1030027</t>
+          <t>1034813</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F17e88edd04557c16658fe6be067fdccf&amp;w=252&amp;s=33144815480d8fa12e2ee385e99d895f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9b88129794dd7576d563514d518de0e9&amp;w=252&amp;s=9280f36c4a468a8ae3568e228564169e</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>b6a1415e6ec13bb2</t>
+          <t>c3c492c79b74c9c9</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2939,11 +2933,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>800 g</t>
-        </is>
-      </c>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2953,41 +2943,41 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Änglamark økologisk survarer</t>
+          <t>Thise økologisk jerseymælk*</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Thise</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>290-580 g</t>
+          <t>1 l</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>266,67. kr/kg</t>
+          <t>15,00. kr/l</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1043929</t>
+          <t>1034811</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6b8954a9b888943a7266c5ec181c80e7%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fce10f80388d16548f2481225da78b515%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6b7bd22abde95cca846b31f04a4e19e0&amp;w=252&amp;s=6ecd5e5fd35b2650ed7b5596acaa94dd</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6a3a11cd7f93e9580ce12c4e1fda0e5d&amp;w=252&amp;s=1144978883651ed928741974483c6665</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>d3e62c0ab5355a59</t>
+          <t>d04a4ab54a7b69b6</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3005,22 +2995,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Xtra hvidløgsbaguette</t>
+          <t>Änglamark økologisk sodavand</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Xtra</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>. 350 g</t>
+          <t>1 l</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>34,29. kr/kg</t>
+          <t>12,00 kr/l</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -3029,17 +3019,17 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1043928</t>
+          <t>1034816</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffacaef37c28af7102a197a9d3f4b4edb&amp;w=252&amp;s=1ae74a109668931e3225c23db6e6060e</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3d2fa2aca69e3cb7aeade1d88fe01898&amp;w=552&amp;s=96f1d2aca110ee957c2518dd3ed2cb78</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>9accce9bc764cb20</t>
+          <t>91506cea2f936c9b</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3057,41 +3047,41 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hans Baer</t>
+          <t>Ânglamark økologisk knækbrød*</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hans</t>
+          <t>Ânglamark</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>. 75 cl</t>
+          <t>. 180 g</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>60,00. kr/l</t>
+          <t>111,11. kr/kg</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1030045</t>
+          <t>1034820</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F85c917f00b6673b1645d48031c315f93&amp;w=252&amp;s=060f6fbc79cec4aca4c690fa2bd8e488</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6b0fb003e336bdbf9aab474d475fb487%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbdf142fcf89f5ae9a90231f8fab14b4c&amp;w=252&amp;s=00236f5b29a7d296c260c227a6c6b978</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>9b32659a30cd32cf</t>
+          <t>9333968cc5d06b7c</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3109,41 +3099,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Thise økologisk ost*</t>
+          <t>Änglamark økologiske havregryn</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thise</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>. 248 g</t>
+          <t>1000 g</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>141,13. kr/kg</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>35</v>
-      </c>
+          <t>11,95. kr/kg</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1043930</t>
+          <t>1034819</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fab85d12b43d3adff431f91e4f70e6e00&amp;w=1152&amp;s=06a9498a62dafafb182984b194ea2872</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F576ace495cace5a0a20dbca35dfd0c92&amp;w=252&amp;s=d15a910c8db9987611aba52e37d66da8</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>cf6d2c9c39343233</t>
+          <t>953c6bc3c3c2d692</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3161,39 +3149,41 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Italiensk pålæg*</t>
+          <t>Änglamark økologisk pizza</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italiensk</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>70-125 g</t>
+          <t>. 370-430 g</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>257,14. kr/kg</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+          <t>75,68. kr/kg</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>28</v>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1053784</t>
+          <t>1034818</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa954f2d4c689d1885cef9cdb93c588ce&amp;w=351&amp;s=4eff4198b5d4e1f4f8875a9ba6e8bfa3</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9f8d275df7180beefa5f87fe9575082a%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F47f95645094e8d71e9519592f89dfa13&amp;w=1152&amp;s=9ee61806c303d9d6fd62db3df77085db</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>c0ba0096d734db3f</t>
+          <t>cbce34349bc63c38</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3211,41 +3201,37 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Änglamark økologisk dansk basilikum</t>
+          <t>Pizzaskærebræt inkl. pizzahjul*</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Pizzaskærebræt</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>. Stk</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>13,00. kr/stk</t>
-        </is>
-      </c>
+          <t>. 1 stk</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1030035</t>
+          <t>1034823</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2ac717dfa77a6f7012af50cd8e86833e&amp;w=552&amp;s=3f3dd8945da0fe7b2bb6734a6cf97465</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb48c952ba86c340cdf7c051074c4b4c3&amp;w=552&amp;s=3693066abf5da156745f17be017c74bb</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96a5699e353a3938</t>
+          <t>85607ae178363d3e</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3263,41 +3249,41 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Danske Dolce Rosso tomater</t>
+          <t>Coop surdejspizzabund*</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Danske</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>. 200 g</t>
+          <t>240 g</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>90,00. kr/kg</t>
+          <t>62,50. kr/kg</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1030036</t>
+          <t>1034822</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbb5ecdb3971fa04a07809db7eb29013b&amp;w=199&amp;s=a92c38e268ce3edb0ea8bd067d1f2b04</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F75347f71d12ba22f2430a3cc41f24182&amp;w=262&amp;s=049804e892ce7214e7338215d4459418</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>d6d2521bad67486c</t>
+          <t>e1b9c6d6394c2372</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3315,12 +3301,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hummus</t>
+          <t>Steff Houlberg topping</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hummus</t>
+          <t>Steff</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3330,26 +3316,26 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>80,00. kr/kg</t>
+          <t>91,43. kr/kg</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1030037</t>
+          <t>1034825</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F344c7cf3d3dad34ea86fd2274ec39cd3%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F923ddd849c294bf5a5c69f9b7dae6740&amp;w=252&amp;s=56bf090795659ddd4a0ce10bcf80d846</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F54a73479af8901f1c32574efc00896ad%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa7ade91c63ad2a682e500b14a15f0681&amp;w=252&amp;s=9ba763d0c770dad600e0a35a225f034f</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>c4c4332b3a3d9dd4</t>
+          <t>ee6d11e23782669a</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3367,41 +3353,41 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Zelected pesto*</t>
+          <t>Nye kartofler</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Zelected</t>
+          <t>Nye</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>190 g</t>
+          <t>. 1 kg</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>105,26. kr/kg</t>
+          <t>14,00. kr/kg</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1030038</t>
+          <t>1034824</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb5179f2bf9fe1e2968f2b53748644152%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F04ef43df5142665581cb55cf8a1645b6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8c71d63cd7b8e192f986c79c2ec630fa%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F67b5eb220a9cf47c85ccf7d9190e3f71&amp;w=252&amp;s=9b3ec5a538b06c9c6f5ad3657abdb646</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1723303248204d6c0d7b96240c69f40b&amp;w=252&amp;s=a38ff7878a1b6dcacad83bf76264841e</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>d0790e86f8fd81f0</t>
+          <t>9ac771dc4e384c27</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3419,41 +3405,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Irma oliven*</t>
+          <t>Italiensk pålæg*</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Italiensk</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>70 g</t>
+          <t>70-125 g</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>142,86. kr/kg</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>10</v>
-      </c>
+          <t>257,14. kr/kg</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1030039</t>
+          <t>1054381</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F873c26b30c556df9207e84a14eccd2d7&amp;w=379&amp;s=32ba1e788dc45a7e52d9585f4507456f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F82d714e58b04907eabab83a3b82e9798&amp;w=351&amp;s=92a6d10695cad901fe0261112fa6ca93</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>911343ecde5654e6</t>
+          <t>c0ba0096d734db3f</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3471,22 +3455,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Legal Zin i boks</t>
+          <t>Urtekram økologisk olivenolie*</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Urtekram</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>. 3 l</t>
+          <t>1000 ml</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>33,00. kr/l</t>
+          <t>99,00. kr/l</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -3495,17 +3479,17 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1030040</t>
+          <t>1034827</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fea125499dc3929b49f0474c4269b594a%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F257a88bfbaa01092cc896df42d03b48a&amp;w=552&amp;s=1324130c5efcde4e161aa8b93f62be53</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5bc097eba2f146c76f4cfc3f2c23af46&amp;w=252&amp;s=7f9bf8cf06382684b765a83d6fc67b71</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>c3c109ff161ce6b4</t>
+          <t>d22d6d8465967993</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3523,41 +3507,41 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cero Coma</t>
+          <t>Coop Grana padano</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cero</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>. 75 cl</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>46,67. kr/l</t>
+          <t>166,67. kr/kg</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1030041</t>
+          <t>1034830</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa9e3f70c7067597fa608f56831a561c0%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F56b2f223767bbed7f878ecb0a7e936ce&amp;w=146&amp;s=931ebdbb695efcfd4bf9a89d616ab7eb</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb410282de7d835fc3d1246d912a1fdc3&amp;w=252&amp;s=32f32f0ad2cc214f9bc1c4cf98c82b98</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>e21144bb3bce49e3</t>
+          <t>855e6ae165b6742a</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3575,41 +3559,41 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Änglamark økologiske grøntsager</t>
+          <t>Coop intenso tomater</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>. 300-450 g</t>
+          <t>. 200 g</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>40,00. kr/kg</t>
+          <t>100,00. kr/kg</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1030052</t>
+          <t>1034829</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=612&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6545e85e589b268e86cb8445f5fb9f0c&amp;w=552&amp;s=eaa9aafd865e64bbda0beebd59f8d9b3</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F12786e818c2859e46d258899a713e352&amp;w=252&amp;s=bde4fee7f98e4f4d0d0dbfbfee9d8a16</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>86b43d0b7943e4ce</t>
+          <t>87cd9293936396cc</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3627,22 +3611,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Änglamark økologiske sandwich kiks</t>
+          <t>Rummo Pasta*</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Rummo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>330 g</t>
+          <t>500 g</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>54,55. kr/kg</t>
+          <t>36,00. kr/kg</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -3651,17 +3635,17 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1030054</t>
+          <t>1034826</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F136aa432715bdb331c52695973098d19&amp;w=90&amp;s=40f25bb9ab159d39c8e726874ab9c2ca</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7afbf74825775fca490ddda832d91afe&amp;w=252&amp;s=5a2b5498205bb8c9f8a85c41dbaa3927</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>c039431b7d5a69d6</t>
+          <t>c69b64663965399a</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3679,41 +3663,41 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Änglamark økologiske spiseklare avocadoer</t>
+          <t>Brema fyldt pasta*</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Brema</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>. 2 stk</t>
+          <t>250-500 g</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>13,00. kr/stk</t>
+          <t>64,00. kr/kg</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1030051</t>
+          <t>1034831</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2b66bdc7acdb162a997b7f9eefe5befc&amp;w=252&amp;s=241e785c92f45ec8fc30b53e86931036</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faa27f6f49403cbd9cf803fc8f9a7d7ce%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe7b88c083b9f2d956453d52a6ea48113%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8c7ee92dc49a87e482496b7372df707b&amp;w=252&amp;s=014c108e471ec6566c037c850770c709</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>cfb3346c52c04b9b</t>
+          <t>8bba5ef1308e290f</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3731,41 +3715,41 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Änglamark smoothies</t>
+          <t>Mutti tomatkonserves*</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Mutti</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>90 g</t>
+          <t>. 400 g</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>55,56. kr/kg</t>
+          <t>25,00. kr/kg</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1030053</t>
+          <t>1034828</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F47f91d50f412780970173e1a0a85ce43&amp;w=252&amp;s=50ff6d08302751560ed7843abd9bb638</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2e7bb17feba573081ac3019ad090581d%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6b8cf7e4abf881820d95fee88139b225%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4529591c8fed0461cdad88f39f8271f4&amp;w=252&amp;s=b086d8ce8111c6b30d25f2a72ea3974f</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>d456202a3eac67bb</t>
+          <t>eef21217790d0d4b</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3783,41 +3767,41 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Knorr færdigret*</t>
+          <t>Corny Big*</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Knorr</t>
+          <t>Corny</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>. 203-321 g</t>
+          <t>. 40-50 g</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>132,35. kr/kg</t>
+          <t>150,00. kr/kg</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1030056</t>
+          <t>1034833</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb9154f4a788cb2f6e80db9e66cad571f&amp;w=552&amp;s=034c9c9c86add945a4b9d59a0a6aa9fc</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F49b605786d73ca2384decbfa6ee97c89&amp;w=552&amp;s=fc703b53b677aa910d3c82c9a20ddd57</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>c64b6cb390c31b2f</t>
+          <t>c0e969d665e43c69</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3835,41 +3819,41 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Livol vitaminer*</t>
+          <t>Skælskør marmelade*</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Livol</t>
+          <t>Skælskør</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>80-150 stk</t>
+          <t>. 265 g</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1,11. kr/stk</t>
+          <t>56,60. kr/kg</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1030057</t>
+          <t>1034835</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fcbdc2824ffc83fcf5bf0f95947a86844&amp;w=552&amp;s=ca77c1dea7cf5c7c90abe172e1e14e61</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6bcf2c74f9b8d532329896e8d7d285ce%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa36ac2f5cae03123d1a78c05113a48ac%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F331c724fd819a2b41487c6a5dde92d25%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffa40fbf66655ffc0e5e9ab6054ae015b&amp;w=252&amp;s=2488c301f4ba3a0240ff9d073703f40f</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>c433633c6c6d36c3</t>
+          <t>c5d032d0784f2fa7</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3887,41 +3871,41 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Yumyum cupnudler*</t>
+          <t>Carletti chokopålæg</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Yumyum</t>
+          <t>Carletti</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>70 g</t>
+          <t>221 g</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>142,86. kr/kg</t>
+          <t>135,75. kr/kg</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1030058</t>
+          <t>1034834</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb4966894c7f72a7506d31dbfc932e7fc%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F27dc7bb77885fb35d7ac69964962f49c%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2445c469308d6e8c04e310933380b31c&amp;w=252&amp;s=86ce5ea903945a53e60dcd5230bbaef8</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa90c2c4a287eb30e0db1f423a1397cb0%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffb4a50d859a405bb308fd5922a1221da&amp;w=252&amp;s=2e9177bf4291b26649c881911d6ad646</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>d4b32b4c6c0dc5f1</t>
+          <t>d1c26ee06ee86e85</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -3939,41 +3923,41 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Coop Tex Mex</t>
+          <t>Valsemøllen mel*</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Valsemøllen</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>. 200-370 g</t>
+          <t>1700-2000 g</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>64,00. kr/kg</t>
+          <t>7,06. kr/kg</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1030059</t>
+          <t>1034886</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F75c8861fa923482ec2e3f821757aa14a&amp;w=252&amp;s=a7ea91c5f677e4cd196730cbad112671</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F45245aa7cafc6008d35cd56b1f571c2e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F26c3bce03269f1b790b95f2e2dded4e6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F94f8684603f324e946da60c1ac847f45&amp;w=552&amp;s=ce5d4fc0d82ef650c4c876696d0be2f1</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>c3cc6d8c32c3961f</t>
+          <t>9189658c638e673f</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -3991,41 +3975,41 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Semper to go grød*</t>
+          <t>Santa Maria Smart Buy krydderier*</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Semper</t>
+          <t>Santa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>120 g</t>
+          <t>. 30-400 g</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>83,33. kr/kg</t>
+          <t>1,333,33. kr/kg</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1030060</t>
+          <t>1034885</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8cc4461bb5f33e6c2e20140ff4cd4d7e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2375a7ee6a6a174725d2b4d451f23959%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff4d7a0ba8c4038274cc6dbc471733f55%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F56d27db8baf4e6138303be3ecb0e6d3e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb9d15707c4873d3d218c21e0d18cc187&amp;w=252&amp;s=3815e6368f79e939acb5180ece05c22d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F03467c1ed0c0afd610cde63359f2dea8&amp;w=552&amp;s=c5bd45ed9b64bb704661cfe22eb7fd50</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>c52c02d37bc3be86</t>
+          <t>c43aa45b3b3ec12b</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4043,41 +4027,41 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>True Dates*</t>
+          <t>Peanutbutter*</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Peanutbutter*</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>100 g</t>
+          <t>1000 g</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>150,00. kr/kg</t>
+          <t>60,00. kr/kg</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1043931</t>
+          <t>1034884</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9a4f1ec8e93ba35a5c56bc6f37a1c533%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F606126ee9b4a1d727f9ca72080281371%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3d3348cce9a201e77c80dd3929c43ec9&amp;w=252&amp;s=3373fe6b5ca9e8ab954e5acacdedf4ed</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8cc00f414ae3aa3061232e5ee2b720b4&amp;w=252&amp;s=22cc0e8566bc7fd6f2d36a88329f4d36</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>8ae27f5571192d0d</t>
+          <t>c47b7b0432fbc8c1</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4095,41 +4079,41 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sæby makrel</t>
+          <t>Kikkoman soyasauce*</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sæby</t>
+          <t>Kikkoman</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>125 g</t>
+          <t>975-1000 ml</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>120,00. kr/kg</t>
+          <t>61,54. kr/l</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1043935</t>
+          <t>1034887</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2d4e9077f20d60434d7b9467d4d94ff1&amp;w=252&amp;s=727d87149fe8c0c1484b75292d335c26</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fde7cecaab8aff4d3930ec5bcd171b674&amp;w=252&amp;s=017aa70732ebf8ca219a7818c9dd6c4f</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>d467679811b71c0f</t>
+          <t>b4e43b3b60859d0f</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4147,41 +4131,41 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Coop tun</t>
+          <t>YUM YUM nudler*</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>168 g</t>
+          <t>360 g</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>107,14. kr/kg</t>
+          <t>88,89. kr/kg</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1030105</t>
+          <t>1034888</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F91ead6bf6f100b050bc95c2c880bd9be&amp;w=252&amp;s=3fb4707b4e205a882f6bf7340308be5b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F74588952e6845016a5d0d5fe75ae0437%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4a42498834202d43130d96a40f78cd57%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffa4e9e2ebeec5683d7b1605741de1182&amp;w=252&amp;s=4cf3342b6e80af049e8856fb295ce3ce</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>989a6765989ae563</t>
+          <t>d678529325dbc493</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4199,41 +4183,41 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Wasa knækbrød dobbeltpack*</t>
+          <t>Bonduelle majs</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wasa</t>
+          <t>Bonduelle</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>. 550 g</t>
+          <t>420 g</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>45,45. kr/kg</t>
+          <t>42,86. kr/kg</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1030025</t>
+          <t>1034889</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faea4197bfaf495efc5937f82b8d4a7e5&amp;w=252&amp;s=e7690373582e3fcd5a97be15149bd20e</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faf60b50696cae2a00ac66f9dcfaa5cd1&amp;w=252&amp;s=d782eff381e7f6fbd37ab41ffeb7e0a4</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>d5372b232a8c6cf2</t>
+          <t>cbe83415d3eac8c5</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4251,41 +4235,41 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Malaco slikpose*</t>
+          <t>Katjes slikpose*</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Malaco</t>
+          <t>Katjes</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>. 192-340 g</t>
+          <t>250 g</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>182,29. kr/kg</t>
+          <t>120,00. kr/kg</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1030064</t>
+          <t>1034838</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F519f8d4c4f77724ef5f2c0709a5cd389&amp;w=235&amp;s=47f544db8f0137f295905681d318328f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F62fbf266b75af0d9b4d396a5d84457e9%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5d577196cb739f1ef5e3447997e4f751%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F483932ede27072eb11d19a11ab0cc3be&amp;w=552&amp;s=dd3845284042013e3b023c75b0bbc022</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>83d476ba0e937cb0</t>
+          <t>c2f13a0ae8fd86e2</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4303,41 +4287,41 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Pingvin slikpose *</t>
+          <t>Selection gaveæske</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pingvin</t>
+          <t>Selection</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>. 80 g</t>
+          <t>175 g</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>125,00. kr/kg</t>
+          <t>228,57. kr/kg</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1030063</t>
+          <t>1034839</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd4e05d879d4630ee3c2d9b603f7d63aa%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0696e52282a6afc48655f320bab083ad%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc6bc085f8c6bfa6ecb1f30121e52ce48%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa1c5be1a0e5b531fe878e660e34a4d1e&amp;w=252&amp;s=14e55f74144d26e4719e157210e69f9b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa5fecb08fde0f18f7c261423c0d2f2c0&amp;w=252&amp;s=e95e7065facc5bc13d1c00cfcc7b100c</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>c07a2f8f68a6d9d0</t>
+          <t>c43b3bc444bb3bc4</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4345,11 +4329,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>80 g</t>
-        </is>
-      </c>
+      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4359,41 +4339,41 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Karen Volf Kagemarked*</t>
+          <t>Samba 6-pak flødeboller*</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Samba</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>. 144-200 g</t>
+          <t>80 g</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>104,17. kr/kg</t>
+          <t>125,00. kr/kg</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1030062</t>
+          <t>1034891</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faac3a6bc81b382d9b22a13b48fadcaf0&amp;w=252&amp;s=fc3c1089c88bcc1aaa212e4d0ba4d022</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F451c3163f12716bd36f6c11bb447fd67%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff1ccd661a460a20f418b322547f40824&amp;w=552&amp;s=e190395991af98bbe740f3d5a1a4dce5</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>ce193166a9ebc619</t>
+          <t>913997968669c7c3</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4411,17 +4391,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Moomin fuldkornskiks*</t>
+          <t>Änglamark økologisk chokolade</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Moomin</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>100 g</t>
+          <t>. 100 g</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4435,17 +4415,17 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>1030066</t>
+          <t>1048631</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F84a43a4fefae23e1d3828c2c33807102%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6029b0d2c102bff39ed93af991b555a9&amp;w=252&amp;s=a3f532a44b9d2d7645452effce83665f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F87c7f4d3534932308db9391aeab5bc50&amp;w=552&amp;s=814552a939de0878d027c97ce114af96</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>c4ec1dca49cb56a6</t>
+          <t>c4736e713cd08dc3</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4463,41 +4443,41 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Fast food slik*</t>
+          <t>Skittles*</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fast</t>
+          <t>Skittles*</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>85-130 g</t>
+          <t>152 g</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>341,18. kr/kg</t>
+          <t>131,58. kr/kg</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1030065</t>
+          <t>1034890</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc3489e6e221895c974d3f6eb9b8579d6&amp;w=252&amp;s=4aba419c71dbefb1bdb83d5ddbed4b65</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4d4f6379ac856fb09649c608eef9d6ef%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1853ef08e8f9aa360bb1dcd24407babd%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd536f69699e3deecc5f746bab0a33c66&amp;w=252&amp;s=5baa6943188aeb69c03c17bb8dd9442d</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>c2f267816ba96e70</t>
+          <t>a6b65f19294d7074</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4515,41 +4495,41 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cirkel Kaffe hele bønner*</t>
+          <t>Karen Volf Kammerjunkere*</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cirkel</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>. 850-900 g</t>
+          <t>250-300 g</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>147,06. kr/kg</t>
+          <t>60,00. kr/kg</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1030113</t>
+          <t>1034893</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff098d3023d97c3cb09737cc489d4f421&amp;w=552&amp;s=b9368390534841e41566a1e8125b5352</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F007545cdd92b0d3dc460b09047240c63%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F949cfdae09037f0d90083a2b8a766859%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F33b245f15dcd39f161a971137fb2e6e4%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F56628fd293c2318cab492a2d44f2fa9e&amp;w=252&amp;s=09d8c93753ba672c22818112cbf00a65</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>cdd1372e48a5ce4a</t>
+          <t>d5da1a487e052d2f</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4567,41 +4547,41 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nutella</t>
+          <t>Coop Corn Puffies</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Nutella</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>350 g</t>
+          <t>80 g</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>111,43. kr/kg</t>
+          <t>175,00. kr/kg</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1030111</t>
+          <t>1034892</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F41e81fc77d907d2ba7512e0bff18041c&amp;w=260&amp;s=33e480d121496c29b986c2b57018cf32</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0a4f6cde8b551486d622d8b046cadc20&amp;w=252&amp;s=0a1d68dbdfbaed6ea8f6b2f00c6c4d63</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>d18400f597eb317e</t>
+          <t>94cb65789066639f</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4619,41 +4599,41 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Rynkeby Nektar</t>
+          <t>Toffypops*</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rynkeby</t>
+          <t>Toffypops*</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1 l</t>
+          <t>120 g</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>14,00. kr/l</t>
+          <t>83,33. kr/kg</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1030068</t>
+          <t>1034894</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0068d27d30cf5fbf539fb565ec3a8a87%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3a9553a8b90de43c9408adcf8bf130eb%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb3d751d721ab79d08daf995b6159e68a&amp;w=552&amp;s=6e81b09ae52aa1f51e5616c2755ccb51</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb9ea36506018afe3db8353098cac2a36%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3c59e19b380b4cfd501692bb048de062&amp;w=252&amp;s=d0319b34299e0b5f814eb872bef7a519</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>d9a571b82f330257</t>
+          <t>c0da3f25c5dac097</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4671,41 +4651,41 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Coca-Cola*</t>
+          <t>Bavaria 6-pak</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Coca-Cola*</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>. 24 x 33 cl</t>
+          <t>6 x 33 cl</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>12,50 kr/l</t>
+          <t>12,63 kr/l</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1030071</t>
+          <t>1034847</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F258d29dfc490bfe068133e2d667bf5ec&amp;w=252&amp;s=5c151849aef47bfad83b69711eae63a8</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fff22e852d0ecaf5dc1b8ad08d560d242%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F919aee1e721d145c596bf110c6c44c7e&amp;w=552&amp;s=22b5565115c21e41d918a70039bc3b95</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>d0603f9d22a3ddf0</t>
+          <t>ee671090611de6be</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4723,41 +4703,41 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tuborg Squash 6-pak*</t>
+          <t>Ready To Drink</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tuborg</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>6 x 33 cl</t>
+          <t>25 cl</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>9,09 kr/l</t>
+          <t>32,00 kr/l</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1030118</t>
+          <t>1048630</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff6290d2f8528f48ddda180acf8be6b8e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faa23c6cbf9d7362551a2f594d5943702%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F46851764f7fa6ef5fd794d5636aa45ea%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F881e72a5a5a46f57bd63628511b2a1c8&amp;w=552&amp;s=7a9809e70fad96b985e4dde94437166b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5f1b91b6972dac153c02bd1a283c9757&amp;w=252&amp;s=8767b014c7922511ef8fa88a8db54f0e</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>96631cc36a943de3</t>
+          <t>c23c2d1f3c2c3b93</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -4775,41 +4755,41 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Blue Keld*</t>
+          <t>Harboe 2 liter</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Harboe</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>. 100 cl</t>
+          <t>. 2 l</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>7,00 kr/l</t>
+          <t>3,00 kr/l</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1030115</t>
+          <t>1034845</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbae5bbb1eec68d7a3dd8c47e3aa252c1%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F62a8192e417b0fdd08de2994d618d985%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6ead742defe5734703c92cacbb8e8586%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd2f8ba9e589e8538e89774c2627e9e78&amp;w=252&amp;s=a4f89cdfe655a890505c31edaa8728e3</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F44c144a3fca9f85df8219558f1e36e8d&amp;w=252&amp;s=e7d641d86bb48369b980a004647b0a43</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>ff4a00b420ff7d28</t>
+          <t>d9a7265626392ad9</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -4827,41 +4807,41 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nailed Energy*</t>
+          <t>Adobe Reserva</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Nailed</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>50 cl</t>
+          <t>. 75 cl</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>16,00 kr/l</t>
+          <t>46,67. kr/l</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1030116</t>
+          <t>1034848</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd940eee91df0bc73183a556c0f560696&amp;w=379&amp;s=53c7364a55d977ef6e2521376ffd76bd</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9c2678478f66d11297b9b3ab99cc507e&amp;w=190&amp;s=28a9e394a0d42e993783ff6dab742f10</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>d1256167652f5a9a</t>
+          <t>b4e151f763a6260e</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -4879,53 +4859,37 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Coop økologiske æbler</t>
+          <t>DAY vinglas 4-pak*</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>DAY</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>. 1 kg</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>16,00. kr/kg</t>
-        </is>
-      </c>
+          <t>51 cl</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1030094</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F401c1961ed4e73834206cfddef5449d2&amp;w=552&amp;s=2ed41d8efa0b643368e7f9a54117756e</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>844e2e6c3565c66f</t>
-        </is>
-      </c>
+          <t>1034857</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>1 kg</t>
-        </is>
-      </c>
+      <c r="L86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4935,41 +4899,37 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Beauvais tomatpuré*</t>
+          <t>Opbevaringsbøtter*</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Beauvais</t>
+          <t>Opbevaringsbøtter*</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>475 g</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>52,63. kr/kg</t>
-        </is>
-      </c>
+          <t>1,2 l</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1030092</t>
+          <t>1034858</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F913892d13d2f0b0aae20eae72ba0730e&amp;w=112&amp;s=4702dce4e7df6fe6c307b4f8a12e8ed3</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F35b1939fc2ecec23ff1a8ebf02f60968&amp;w=552&amp;s=cf6e072ce956c684357e82885b208e17</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>c49795d1d0c6479e</t>
+          <t>c16a37a548cb9d27</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -4987,41 +4947,37 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Coop revet mozzarella</t>
+          <t>Krydderiglas 12-pak*</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Krydderiglas</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>200 g</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>60,00. kr/kg</t>
-        </is>
-      </c>
+          <t>12 stk</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1030095</t>
+          <t>1034855</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F99652bf084bbd6f1fbff529ea3fbe870&amp;w=252&amp;s=1475f290c8c2937eb9469b5a16b5b328</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe06a384f29356285f0114995e1fca021&amp;w=252&amp;s=f9738c02d3539f7080e783fe2bc567e3</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>c4c969969da6d3c8</t>
+          <t>d5e92e0863952bb3</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5039,41 +4995,41 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Xtra skinke strimler</t>
+          <t>Designservietter*</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Xtra</t>
+          <t>Designservietter*</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>200 g</t>
+          <t>. 3-l</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>60,00. kr/kg</t>
+          <t>0,50. kr/stk</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1030093</t>
+          <t>1034854</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff7e8fca131ace1e16248dcfa77b9ff75&amp;w=252&amp;s=8b5fdc98fc3512000bc0814db55fd6c7</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1f13272fe981edb036e4b1f2aa31ce27&amp;w=252&amp;s=7a7e0625f4ba5a21ed978191a8f2ee3b</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>856dc03b93b613cb</t>
+          <t>b5f74a080e6e91d5</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5091,41 +5047,37 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Coop fersk dej</t>
+          <t>Køkkenudstyr*</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Køkkenudstyr*</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>. 275-400 g</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>18,18. kr/kg</t>
-        </is>
-      </c>
+          <t>700 ml</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1030091</t>
+          <t>1034859</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdf722f8126c141319d9548b97789b5ad&amp;w=1152&amp;s=6e368f7d0d6d6c707d1f0eb17e3fb69f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbf9302d396aa888644019c8fcb511198&amp;w=252&amp;s=688908da2710145a5e24d7a441c03962</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>93cb6466643c6cce</t>
+          <t>cfce3130cdd93033</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5134,6 +5086,1270 @@
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Quiltet tæppe*</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Quiltet</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>. 1 stk</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="n">
+        <v>60</v>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>1034864</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F29cc953986ea2797fa6f8cbd5415b25c&amp;w=352&amp;s=f352071aa0695f772221f91b98854a11</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>d5d12afc4e902be8</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Pude*</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Pude*</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>. 1 stk</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="n">
+        <v>50</v>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>1034865</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb1c86eeeab3494dce4a4028c124bda9e&amp;w=352&amp;s=fc4a1e693690ec27631a80d216615eb2</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>95f3680e6f0c2e39</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Dug*</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Dug*</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>. 1 stk</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="n">
+        <v>85</v>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>1034866</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F52163bcdddda26c466610925a4ddae09&amp;w=352&amp;s=f972d72423cf7322833ebcf62f562adf</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>d56a3d35367a2425</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Nordicgrill engangsgrill*</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Nordicgrill</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="n">
+        <v>25</v>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>1034863</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Sanex roll-on*</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Sanex</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>50 ml</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="n">
+        <v>16</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>1034871</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fcead20adf02eac89758dc8b6977ce4fa%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8b0f1dbf7ae065c127528bc84bac7749%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5466b95be12ebef81b530342f60cab43&amp;w=552&amp;s=30b35184dc45355fcb178db5eaf193ac</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>c16b690b363e3665</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Scholl fodpleje*</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Scholl</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>60 ml</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>650,00 kr/l</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>39</v>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>1034868</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F22ebec14d3978e9a0c19f1063f57fabd&amp;w=252&amp;s=bac248120cd79c34d467cdbc25ed145b</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>83f4784b54094faf</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>365 Minirisk personlig pleje</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>. 50-200 ml</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>200,00. kr/l</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>10</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>1034899</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F97acebc1be855f7fe9b54d30f69eb3e1&amp;w=252&amp;s=be1890c50cba1cf4ba48ccd7158c3cc8</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>94d33c958c1cdb3c</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Nutramino protein wafer*</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Nutramino</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>35-39 g</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>285,71. kr/kg</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>10</v>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>1034902</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faf1814139456acde7fa4d1bdcf713724%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F962c989315cb630c65684df586a6c841%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc24d95ea550341865becb38b1e78f222&amp;w=552&amp;s=a36dbc573f2e472b497f055cbe4ec528</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>dfb62009f8f0c665</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Schulstad Signaturbrød</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Schulstad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>. 600-850 g</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>26,67. kr/kg</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>16</v>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1034873</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=612&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdb89ee4ccb039a305fb4773d5311a2ca&amp;w=552&amp;s=b8e48b5fa4d6c56bd660394e69864572</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>cf9c3c6dc792902c</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Fjerkræs kyllingepålæg*</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Fjerkræs</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>80 g</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>175,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>14</v>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>1034874</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5719b5ea4bfac57e784e95159d60dce9&amp;w=552&amp;s=c461e15efa9448d72354e0b67cd77b84</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>9b26cc8ccccc6dcc</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Innocent kids smoothies</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Innocent</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>4 x 150 ml</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>33,33. kr/l</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>20</v>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>1034876</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7c24cf5901bfcdfc19847ff5fc2c1518&amp;w=252&amp;s=100ce1f7f7e33e303c31a9e6427df648</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>85976c9f3cc81d8c</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Stjernehaps*</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Stjernehaps*</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>100 g</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>200,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>20</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>1034875</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7731530d602b354fee7eec75418f6bdb&amp;w=252&amp;s=f042cbb0d14439a092535b2a805cf7fe</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>92939e6a67662cc9</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Klovborg skiveost</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Klovborg</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>200-240 g</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>110,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>22</v>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>1034877</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faa4e03edf4be7c509942c6da61f29316&amp;w=315&amp;s=e0680be48c9625b52741ae3aa5bb9453</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>90585dd24f9e1e69</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Irma pålægssalater*</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>150-175 g</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>166,67. kr/kg</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>25</v>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>1034955</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F91523bcb85ccdd30cd56e43b4ea830de&amp;w=552&amp;s=019a9893482ac2a0c2a16c29e3321ec4</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>d097076a171b7a2d</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Irma rejer*</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>. 150 g</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>166,67. kr/kg</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>25</v>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>1034958</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb0184c196a7eec7d75ad28f2d59e64e5&amp;w=236&amp;s=3bbb5bd38d993ce5b54d4d3820ec2646</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>c53d7ac1346a6a96</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Irma karklude 2-pak*</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="n">
+        <v>49</v>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1034957</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5c7d946f1c43c1d8df40ae8670ea3b80&amp;w=476&amp;s=2af3292ace68679b45bd67e82dbe4e11</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>e4a41a5c4d1f4b3b</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Irma økologiske pølser*</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>240-280 g</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>145,83. kr/kg</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>35</v>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>1034963</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F353894a931dc477df51e47b557306229&amp;w=552&amp;s=e8623e598f6dfa57686dd54811332e1f</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>8e1f71e21e9f8b08</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Irma brioche fastfoodbrød</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>250-270 g</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>88,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>22</v>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>1034961</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F894e784a8aa7168a2956c6d43566d966&amp;w=252&amp;s=8df21a4f731af7b85be48f16e2ed4d5c</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>ba1845e7ee51a82e</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Irma oliven*</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>70 g</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>142,86. kr/kg</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>10</v>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>1034964</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe588e54bbc22f92805dfb99bfa572ffe&amp;w=552&amp;s=13d5f17f282449014739bcf9a7b2f679</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>d1151fec6e6b2305</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Irma danske lakseportioner</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>. 200 g</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>245,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>49</v>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>1034967</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F12538a579cd59f7bf75ef8c1cc10c294&amp;w=252&amp;s=68757a8eab939fd9bdf9317db70b73f7</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>a851779c5f2788d8</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Irma islandsk flagesalt*</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>250 g</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>112,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>28</v>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>1034965</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6e564b25154bdfe1e2acc19d5f565276&amp;w=252&amp;s=6eccfc2752dbcf8377eb8797a08b24a9</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>a5ca64cb37340b37</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Irma økologisk pizza*</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>. 400 g</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>137,50. kr/kg</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>55</v>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>1034968</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fac0ea3352a57bc3330dfcf0394155979&amp;w=494&amp;s=af997c36ae1b13af565b8d189269ee00</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>d3934c9159b033fc</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Irma frugttærte*</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>. 430 g</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>116,67. kr/kg</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>49</v>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>1034969</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fda36869ad20d4c012eb3e098e1cba101&amp;w=552&amp;s=e833fa48a74a558bb5e01adf92134368</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>95356ac8b52fd2d0</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Irma marcipanbrød*</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>35 g</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>342,86. kr/kg</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>12</v>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>1034970</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F516aee6d859dccdeff91abcd2d2ea4ac&amp;w=552&amp;s=76a6844ca773a26d8251e6c0909a6710</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>cb9461d936c963cc</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Irma lakridskugler*</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>110 g</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>318,18. kr/kg</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>35</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1034972</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb57f778bb724441ef0985a38c33e254c&amp;w=252&amp;s=53dca89db47fa4709a0a14a3e58cf5eb</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>c334343c3c37db38</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Xlsx filer/365Discount_produkter.xlsx
+++ b/Xlsx filer/365Discount_produkter.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L115"/>
+  <dimension ref="A1:L153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -611,41 +611,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rød peber</t>
+          <t>Coca-Cola, Fanta, Squash eller Red Bull*</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rød</t>
+          <t>Coca-Cola,</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>. Stk</t>
+          <t>. 25-150 cl</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6,00. kr/stk</t>
+          <t>40,00 kr/l</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1034879</t>
+          <t>1034754</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff4f26920b405ae8245c6e2cb43b349bb&amp;w=552&amp;s=9b6fb29a42c62edf6eed4778f2f460c7</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7bfe86f6959f9205c34fb572f6595bd5&amp;w=252&amp;s=04e4abfbea169f002eceb310f27f7452</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>c74c6c3c34da3a93</t>
+          <t>9b6a66316da5921b</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -663,41 +663,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hakket kylling 7-10%</t>
+          <t>Conde Pinel eller The Flag i boks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hakket</t>
+          <t>Conde</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1000 g</t>
+          <t>. 3 L</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>45,00. kr/kg</t>
+          <t>29,67. kr/l</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1034881</t>
+          <t>1034750</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff28d7d9d01a0e4b2405a2546783cd875&amp;w=552&amp;s=a06578556e71a9b0431edf2cbb3d2ddb</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2192bb15694727632e7a4340050a4ce4&amp;w=252&amp;s=4c25bd8940aa5df688ff5dfa8caef87e</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9533c799cec431cc</t>
+          <t>d2e42d1b9e99c2e4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -705,11 +705,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1000 g</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -719,41 +715,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capri-Sun*</t>
+          <t>Rød peber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Capri-Sun*</t>
+          <t>Rød</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>. 10 x 20 cl</t>
+          <t>. Stk</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10,00. kr/l</t>
+          <t>6,00. kr/stk</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1034882</t>
+          <t>1034879</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4a08f9cbaae5c886af64ac41c551b99b%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff1b440bedc249996de2221c82abdfb60%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9aa954c8eee819cbfacbf8572f87943b&amp;w=252&amp;s=062ffbaea09ffc5de93c122ed15364c8</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff4f26920b405ae8245c6e2cb43b349bb&amp;w=552&amp;s=9b6fb29a42c62edf6eed4778f2f460c7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>907a580b0ff578bc</t>
+          <t>c74c6c3c34da3a93</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -771,41 +767,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cheasy yoghurt</t>
+          <t>Hakket kylling 7-10%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cheasy</t>
+          <t>Hakket</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1 kg</t>
+          <t>1000 g</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10,00. kr/kg</t>
+          <t>45,00. kr/kg</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1034757</t>
+          <t>1034881</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3abd256bb1135bac04b28dd288539d33&amp;w=252&amp;s=4c3d5a411f634c5c545e2ff960b87b73</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff28d7d9d01a0e4b2405a2546783cd875&amp;w=552&amp;s=a06578556e71a9b0431edf2cbb3d2ddb</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>a0d01f2f7eca6a2c</t>
+          <t>9533c799cec431cc</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -813,7 +809,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1000 g</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -823,41 +823,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kims chips*</t>
+          <t>Capri-Sun*</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kims</t>
+          <t>Capri-Sun*</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>. 75-95 g</t>
+          <t>. 10 x 20 cl</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>133,33. kr/kg</t>
+          <t>10,00. kr/l</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1034758</t>
+          <t>1034882</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=612&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4f9ea6225e9e0333fa389283b4aa0048&amp;w=552&amp;s=797c95dc904ad4eee6301af9c5b2b5e7</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4a08f9cbaae5c886af64ac41c551b99b%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff1b440bedc249996de2221c82abdfb60%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9aa954c8eee819cbfacbf8572f87943b&amp;w=252&amp;s=062ffbaea09ffc5de93c122ed15364c8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>e5b73ee162c80c72</t>
+          <t>907a580b0ff578bc</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -875,41 +875,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cheasy hytteost</t>
+          <t>Merrild eller Lavazza formalet kaffe eller Merrild instant kaffe*</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cheasy</t>
+          <t>Merrild</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>250 g</t>
+          <t>. 120-500 g</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>40,00. kr/kg</t>
+          <t>491,67. kr/kg</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1034756</t>
+          <t>1034751</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F37ada5ab0761a82634016cd2a9524b86&amp;w=552&amp;s=1d1efce31ed7a4444cbe5575f3739dab</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc4eb4a300cc772dc11198f8f595f7b43&amp;w=252&amp;s=c333410e8bd89c2973922b589637c535</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>93b43a338e1c8ece</t>
+          <t>95331e67264c5c6e</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -927,41 +927,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sun Lolly</t>
+          <t>Cheasy yoghurt</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Cheasy</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>. 8 x 60 ml</t>
+          <t>1 kg</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>29,17. kr/l</t>
+          <t>10,00. kr/kg</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1034760</t>
+          <t>1034757</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5f9c3d27e7347df3b966e8b09b45de00&amp;w=252&amp;s=f71750aeba5175fe9b0d398ae6226c34</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3abd256bb1135bac04b28dd288539d33&amp;w=252&amp;s=4c3d5a411f634c5c545e2ff960b87b73</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8570362ec1d93db3</t>
+          <t>a0d01f2f7eca6a2c</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -979,41 +979,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gøl pølser*</t>
+          <t>Kims chips*</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gøl</t>
+          <t>Kims</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>339-420 g</t>
+          <t>. 75-95 g</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>85,55. kr/kg</t>
+          <t>133,33. kr/kg</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1034759</t>
+          <t>1034758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0fb8165e43b965e3eb1c816ab8b4be16&amp;w=302&amp;s=4dda9246ca6ecb4cb38dbe5759df8e29</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=612&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4f9ea6225e9e0333fa389283b4aa0048&amp;w=552&amp;s=797c95dc904ad4eee6301af9c5b2b5e7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>93cd3cb61e916a68</t>
+          <t>e5b73ee162c80c72</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1031,41 +1031,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Coop paneret kylling</t>
+          <t>Cheasy hytteost</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Cheasy</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>. 200-250 g</t>
+          <t>250 g</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>60,00. kr/kg</t>
+          <t>40,00. kr/kg</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1034762</t>
+          <t>1034756</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=612&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F73ace2b214724147207c58382cdc4c2a%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2c79a44550caa29c0e995844b2f60bd2&amp;w=552&amp;s=5c24a03c85c259ee6dc2a011252c7767</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F37ada5ab0761a82634016cd2a9524b86&amp;w=552&amp;s=1d1efce31ed7a4444cbe5575f3739dab</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>917c65c3fed43103</t>
+          <t>93b43a338e1c8ece</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1083,41 +1083,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Oreo*</t>
+          <t>Danonino eller Actimel*</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oreo*</t>
+          <t>Danonino</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>154-157 g</t>
+          <t>300-400 g</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>77,92. kr/kg</t>
+          <t>33,33. kr/kg</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1034763</t>
+          <t>1048625</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1d4bee6d0854cc9fbaf1ff129b3e765b&amp;w=252&amp;s=d1b9710425e4ae45955ea321ccd1d28d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd763bfa2b29f4b8b0cc19fdbd92e66d2&amp;w=252&amp;s=f73e583167c634a8297981a29f649137</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>d5b67f427a920b28</t>
+          <t>c46a6ed40b991bf8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1135,41 +1135,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Haribo slikpose*</t>
+          <t>Sun Lolly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Haribo</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>. 120 g</t>
+          <t>. 8 x 60 ml</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>100,00. kr/kg</t>
+          <t>29,17. kr/l</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1034764</t>
+          <t>1034760</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb7e08be0c2ee7405733e2aeae96ff5fb&amp;w=227&amp;s=798280b7ab190580d963f65bbbdbbeff</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5f9c3d27e7347df3b966e8b09b45de00&amp;w=252&amp;s=f71750aeba5175fe9b0d398ae6226c34</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>93c8b1a1174fb8ec</t>
+          <t>8570362ec1d93db3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1187,39 +1187,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Coop hakket oksekød 14-18%</t>
+          <t>Gøl pølser*</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Gøl</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>339-420 g</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>94,88. kr/kg</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>85,55. kr/kg</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>29</v>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1034770</t>
+          <t>1034759</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F68d27b6752224a330f520bf15e8c96cd&amp;w=552&amp;s=282a880255a6bccef3ee3d86fe4ceb3b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0fb8165e43b965e3eb1c816ab8b4be16&amp;w=302&amp;s=4dda9246ca6ecb4cb38dbe5759df8e29</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>c33834cf66cc6533</t>
+          <t>93cd3cb61e916a68</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1237,7 +1239,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Coop medister</t>
+          <t>Coop paneret kylling</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1247,31 +1249,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>500 g</t>
+          <t>. 200-250 g</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>48,00. kr/kg</t>
+          <t>60,00. kr/kg</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1034767</t>
+          <t>1034762</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F86b64aa7103126d94c644b20d3e333e9&amp;w=552&amp;s=67b12b42c1b5e61346304901cc799760</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=612&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F73ace2b214724147207c58382cdc4c2a%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2c79a44550caa29c0e995844b2f60bd2&amp;w=552&amp;s=5c24a03c85c259ee6dc2a011252c7767</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>c7649a934c9a6d6c</t>
+          <t>917c65c3fed43103</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1289,41 +1291,41 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Coop nakkefilet</t>
+          <t>Knorr sauce, bouillon eller fond du chef*</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Knorr</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1100 g</t>
+          <t>. 57-112 g</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>71,82. kr/kg</t>
+          <t>175,44. kr/kg</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1034774</t>
+          <t>1034761</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fce0c16a9ccd38c85bf332fae872dc6de&amp;w=252&amp;s=14a5b2b4dbca27fcfb2f1f698cd7b590</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb9c97d33fce2b0e7eb985c391167a7e0&amp;w=552&amp;s=99f99ad6e28d1eac1494fe6d9fb6d8f0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>d0364b9d6a383b33</t>
+          <t>9b92396333933399</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1341,41 +1343,41 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jensens Køkken sauce*</t>
+          <t>Oreo*</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jensens</t>
+          <t>Oreo*</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>250-350 ml</t>
+          <t>154-157 g</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>64,00. kr/l</t>
+          <t>77,92. kr/kg</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1034766</t>
+          <t>1034763</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa42f5f4cddb7a5b0b7f4a36cc0310424%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc9888fae13143e2e1659c04849666f4e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fabe5805063ea864a9be2b607288c7fcb%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffce21d15c7c1218cab8c5208a999d1ea&amp;w=252&amp;s=fb39717525de433eba634520448c5f57</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1d4bee6d0854cc9fbaf1ff129b3e765b&amp;w=252&amp;s=d1b9710425e4ae45955ea321ccd1d28d</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>da5e4e392025bf29</t>
+          <t>d5b67f427a920b28</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1393,7 +1395,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Coop marineret flanksteak med oregano og hvidløg</t>
+          <t>Coop biksemad, Chicken tandoori, Bami goreng eller Steff Houlberg pølsemix</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1403,31 +1405,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>. 400-500 g</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>220,00. kr/kg</t>
+          <t>50,00. kr/kg</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1034768</t>
+          <t>1034765</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdb575c8a9c5b9cbb4df00c436965d35f&amp;w=252&amp;s=1e6a0991c66c8dd5ce4cb818e49312fc</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbbd0860f4d7d10b5810b0982851e5f53&amp;w=252&amp;s=ed4c0a574391b2c07f8a61c8dbc87ae0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>eada01351ff0744b</t>
+          <t>c5db7141c9d03f62</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1445,39 +1447,41 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hele kyllingelår</t>
+          <t>Haribo slikpose*</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hele</t>
+          <t>Haribo</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2000 g</t>
+          <t>. 120 g</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>34,50. kr/kg</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>100,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>12</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1054380</t>
+          <t>1034764</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F70d4c5923fe81116834fdc7090c29883&amp;w=1152&amp;s=165b3e82de12b47e897ea7f98f2b17c8</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb7e08be0c2ee7405733e2aeae96ff5fb&amp;w=227&amp;s=798280b7ab190580d963f65bbbdbbeff</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>996636396399cc33</t>
+          <t>93c8b1a1174fb8ec</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1495,41 +1499,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Langelænder pølser*</t>
+          <t>Coop hakket oksekød 14-18%</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Langelænder</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1400-1500 g</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>63,57. kr/kg</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>89</v>
-      </c>
+          <t>94,88. kr/kg</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1034778</t>
+          <t>1034770</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff632f5dfc3f4f74b2a16f1fbb17cd7c7%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F29293cdb14dddf70c5d42c8ca76542a1%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe3ec527568134be7f0aa6bbc5295cd33&amp;w=552&amp;s=594d36916f04d1ac7404d1698b9da8b6</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F68d27b6752224a330f520bf15e8c96cd&amp;w=552&amp;s=282a880255a6bccef3ee3d86fe4ceb3b</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>df4920b60e27d359</t>
+          <t>c33834cf66cc6533</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1547,7 +1549,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Coop feta*</t>
+          <t>Coop medister</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1557,31 +1559,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>500 g</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>120,00. kr/kg</t>
+          <t>48,00. kr/kg</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1034776</t>
+          <t>1034767</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1631bb3d477c0a26b19630fdba66d001&amp;w=266&amp;s=d57ebff16390630f7b59bdf14d0b1573</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F86b64aa7103126d94c644b20d3e333e9&amp;w=552&amp;s=67b12b42c1b5e61346304901cc799760</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>820f3dda703535ab</t>
+          <t>c7649a934c9a6d6c</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1599,41 +1601,41 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Courget</t>
+          <t>Coop nakkefilet</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Courget</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>. Stk</t>
+          <t>1100 g</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6,00. kr/stk</t>
+          <t>71,82. kr/kg</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1034781</t>
+          <t>1034774</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9a20dd71fa9720adf8fa2389d9a028c7&amp;w=252&amp;s=e9b076d251662a7c61ef1234090348a5</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fce0c16a9ccd38c85bf332fae872dc6de&amp;w=252&amp;s=14a5b2b4dbca27fcfb2f1f698cd7b590</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>a5bf5240abbf1541</t>
+          <t>d0364b9d6a383b33</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1651,41 +1653,41 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Heinz ketchup*</t>
+          <t>Jensens Køkken sauce*</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Heinz</t>
+          <t>Jensens</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>570 g</t>
+          <t>250-350 ml</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>31,58. kr/kg</t>
+          <t>64,00. kr/l</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1034779</t>
+          <t>1034766</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Feb4e3ba7546b85d7dd58d4651e8aa540&amp;w=252&amp;s=f810dc27e66c683b693b5573a555d15d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa42f5f4cddb7a5b0b7f4a36cc0310424%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc9888fae13143e2e1659c04849666f4e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fabe5805063ea864a9be2b607288c7fcb%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffce21d15c7c1218cab8c5208a999d1ea&amp;w=252&amp;s=fb39717525de433eba634520448c5f57</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>cd39cccc3399634c</t>
+          <t>da5e4e392025bf29</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1703,41 +1705,41 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Graasten kartoffelsalat*</t>
+          <t>Coop marineret flanksteak med oregano og hvidløg</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Graasten</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>50,00. kr/kg</t>
+          <t>220,00. kr/kg</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1034777</t>
+          <t>1034768</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa853f748eee0cd59921a8f4b5466dfdd%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0b756c550e7b3b51470e103555613d98&amp;w=252&amp;s=5a7adc542d5cdc7cde602f87a2f10d60</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdb575c8a9c5b9cbb4df00c436965d35f&amp;w=252&amp;s=1e6a0991c66c8dd5ce4cb818e49312fc</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>9c6c7290eb959c66</t>
+          <t>eada01351ff0744b</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1755,41 +1757,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Salat, skyllet og klar til brug</t>
+          <t>Coop cevapcici okse/gris eller crunchy rools</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Salat,</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>75 g</t>
+          <t>300-360 g</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>133,33. kr/kg</t>
+          <t>96,67. kr/kg</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1034780</t>
+          <t>1059809</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fda81ed2a56f5204074b2a971627e304b&amp;w=252&amp;s=44e15cbdc3d402bd106055a8a9de0a89</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc7228f4a4f03129ac89cab1248277ae3%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F06be17d4badde00de83de30a0014214a&amp;w=252&amp;s=0c9684a72e98ad394d14424408e4c06a</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>9b52642d65d38b78</t>
+          <t>cc4731a066bbb1d3</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1807,33 +1809,41 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Änglamark økologiske bananer</t>
+          <t>Xtra! kyllingebryst eller -inderfilet</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Änglamark</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+          <t>Xtra!</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>600 g</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>81,67. kr/kg</t>
+        </is>
+      </c>
       <c r="F27" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1034783</t>
+          <t>1034775</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9470a954e7071e9384ee9336745e0aef&amp;w=552&amp;s=eba33f6415b0299d6661686196888e6b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F30eed01d02ac300fab5d15f2ba81dceb&amp;w=552&amp;s=3e838b465ac4e4e86795545266decad1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>9473722e4b8969b5</t>
+          <t>d91a26e5f30acc35</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1851,41 +1861,41 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Xtra! kyllingebryst med citron/rosmari, bbq eller Coop marineret grillspyd af gris med grønt</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Xtra!</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>. Stk</t>
+          <t>280-375 g</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10,00. kr/stk</t>
+          <t>125,00. kr/kg</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1034784</t>
+          <t>1034771</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F48b9ceb46bae7e33ea968eebadd07acc&amp;w=552&amp;s=7bcf12db1501ea9352112357e0026345</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb0093dbacfec881ba058bfef5d119f54&amp;w=552&amp;s=d60f7cc4ba372270419cb65d62e4ddc6</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>9a9849696d733533</t>
+          <t>cf2c6949cd4c9c93</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1903,41 +1913,41 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Galiamelon</t>
+          <t>Coop kylling i tern eller strimler</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Galiamelon</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>. Stk</t>
+          <t>250 g</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20,00. kr/stk</t>
+          <t>128,00. kr/kg</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1034786</t>
+          <t>1034773</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F425ae8e87f14ed5299faf279264cbe1c&amp;w=252&amp;s=e7556ac2a594122320f70828db04489b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F045e5edb73ea5ca5975d9dad435f65de%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0d6373e317edf0694a02490984759186&amp;w=552&amp;s=a268f0c6609f975ee807edf28ec16a5b</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>958356cd6a0e6a3e</t>
+          <t>8c4f59e05de264ae</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1955,41 +1965,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Formodne avocadoer</t>
+          <t>Hele kyllingelår</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Formodne</t>
+          <t>Hele</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>. 3 stk</t>
+          <t>2000 g</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6,00. kr/stk</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>18</v>
-      </c>
+          <t>34,50. kr/kg</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1034787</t>
+          <t>1054380</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7a56aa49f5d8aa140550a61ff3db4a36&amp;w=252&amp;s=2d678dc0fb3caf59015a1fe622b5207f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F70d4c5923fe81116834fdc7090c29883&amp;w=1152&amp;s=165b3e82de12b47e897ea7f98f2b17c8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>939c96e69ac99c8a</t>
+          <t>996636396399cc33</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1997,11 +2005,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>3 stk. pr.</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2011,41 +2015,41 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Irma blåbær</t>
+          <t>Langelænder pølser*</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Langelænder</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>. 200 g</t>
+          <t>1400-1500 g</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>160,00. kr/kg</t>
+          <t>63,57. kr/kg</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1048626</t>
+          <t>1034778</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F49f214345531ed36643e7b3bdf4522c5&amp;w=385&amp;s=59c59635ab89a5922ba0046cae6214cf</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff632f5dfc3f4f74b2a16f1fbb17cd7c7%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F29293cdb14dddf70c5d42c8ca76542a1%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe3ec527568134be7f0aa6bbc5295cd33&amp;w=552&amp;s=594d36916f04d1ac7404d1698b9da8b6</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>d7180a3fd0e3423f</t>
+          <t>df4920b60e27d359</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2063,41 +2067,41 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aalbæk spegepølse i skiver</t>
+          <t>Coop feta*</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Aalbæk</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>60 g</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>266,67. kr/kg</t>
+          <t>120,00. kr/kg</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1034791</t>
+          <t>1034776</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa349eb2605ee926eeefcda315387cf5b&amp;w=252&amp;s=b78352d25f74c098091b5ee6ff97c3eb</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1631bb3d477c0a26b19630fdba66d001&amp;w=266&amp;s=d57ebff16390630f7b59bdf14d0b1573</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>db0c64323aca6be3</t>
+          <t>820f3dda703535ab</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2115,41 +2119,41 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kohberg hvedebrød</t>
+          <t>Courget</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kohberg</t>
+          <t>Courget</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>. 380-500 g</t>
+          <t>. Stk</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>47,37. kr/kg</t>
+          <t>6,00. kr/stk</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1034792</t>
+          <t>1034781</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F61f165afb25f96bca795b4eb565a21b5%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F59b6625d45ec457bbe40c16fbd1e1515%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F16b7c76c88204a13873a2802b58451bf&amp;w=252&amp;s=3e8269d2fd3b5389bccf12aec636a625</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9a20dd71fa9720adf8fa2389d9a028c7&amp;w=252&amp;s=e9b076d251662a7c61ef1234090348a5</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>95701aaf7f8a2c1c</t>
+          <t>a5bf5240abbf1541</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2167,39 +2171,41 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tulip bacon 3-pak</t>
+          <t>Heinz ketchup*</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tulip</t>
+          <t>Heinz</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3 x 125 g</t>
+          <t>570 g</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>93,20. kr/kg</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>31,58. kr/kg</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>18</v>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1034793</t>
+          <t>1034779</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F75b95e65a141d19fcdc8214b35ce1c38&amp;w=252&amp;s=070824199a471d1ebe080f8bd9f19148</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Feb4e3ba7546b85d7dd58d4651e8aa540&amp;w=252&amp;s=f810dc27e66c683b693b5573a555d15d</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>a76658991962b69d</t>
+          <t>cd39cccc3399634c</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2217,12 +2223,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Stryhns leverpostej*</t>
+          <t>Graasten kartoffelsalat*</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Stryhns</t>
+          <t>Graasten</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2241,17 +2247,17 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1034790</t>
+          <t>1034777</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff8c35430559f4260c1952eb74aa237dd%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fcbe2e3d822215ecfd7e82285a8bec5d6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F494b93f91e0066315bf3e863ea7cc049&amp;w=252&amp;s=3cf177ac48dd630654fe2cf99013401e</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa853f748eee0cd59921a8f4b5466dfdd%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0b756c550e7b3b51470e103555613d98&amp;w=252&amp;s=5a7adc542d5cdc7cde602f87a2f10d60</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>d1f7d58a207aeaa0</t>
+          <t>9c6c7290eb959c66</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2269,41 +2275,41 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Amanda gulfinnet tun*</t>
+          <t>Salat, skyllet og klar til brug</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Salat,</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>105 g</t>
+          <t>75 g</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>114,29. kr/kg</t>
+          <t>133,33. kr/kg</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1034795</t>
+          <t>1034780</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F42d8e8d3f06ef567b299df8126a250be%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa81e23b12d6f78c8737bafbcf8b3818c&amp;w=552&amp;s=d37e89718f195457a143be1e9a0cf206</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fda81ed2a56f5204074b2a971627e304b&amp;w=252&amp;s=44e15cbdc3d402bd106055a8a9de0a89</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>80975739627e7938</t>
+          <t>9b52642d65d38b78</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2321,41 +2327,33 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Royal Greenland Diskobay kutterrejer</t>
+          <t>Änglamark økologiske bananer</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Royal</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>230 g</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>195,65. kr/kg</t>
-        </is>
-      </c>
+          <t>Änglamark</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1048628</t>
+          <t>1034783</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdf0ab0b622487d13c15db283840ad55c&amp;w=252&amp;s=711016fd5698a5c51367fbcc65279e65</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9470a954e7071e9384ee9336745e0aef&amp;w=552&amp;s=eba33f6415b0299d6661686196888e6b</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>c14c16971e7b6b4c</t>
+          <t>9473722e4b8969b5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2373,41 +2371,41 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Glyngøre kullerfilet</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Glyngøre</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>225 g</t>
+          <t>. Stk</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>173,33. kr/kg</t>
+          <t>10,00. kr/stk</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1034798</t>
+          <t>1034784</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0ec9d9a900838a72df69ef6eacfea760&amp;w=252&amp;s=afc7d443861039b8f6640b762f496b11</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F48b9ceb46bae7e33ea968eebadd07acc&amp;w=552&amp;s=7bcf12db1501ea9352112357e0026345</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>c41f2ee43113973b</t>
+          <t>9a9849696d733533</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2425,41 +2423,41 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Glyngøre lakseportioner</t>
+          <t>Galiamelon</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Glyngøre</t>
+          <t>Galiamelon</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>225 g</t>
+          <t>. Stk</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>191,11. kr/kg</t>
+          <t>20,00. kr/stk</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1034794</t>
+          <t>1034786</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa0c58b46fbce52b47359e1e0d7f8be5e&amp;w=418&amp;s=439e14f261c6dc86b22928fad4d81ad1</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F425ae8e87f14ed5299faf279264cbe1c&amp;w=252&amp;s=e7556ac2a594122320f70828db04489b</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>c03b6cdf103bd4cc</t>
+          <t>958356cd6a0e6a3e</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2477,41 +2475,41 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Polar is</t>
+          <t>Formodne avocadoer</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Formodne</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>. 1 l</t>
+          <t>. 3 stk</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20,00. kr/kg</t>
+          <t>6,00. kr/stk</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1034804</t>
+          <t>1034787</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fee3917f0d07d64d3df9dab6f111f80c7%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdb54330ce073edcacd43d64a718ed9dd&amp;w=552&amp;s=4db1fabe17ba954a9d79d23b6d198d18</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7a56aa49f5d8aa140550a61ff3db4a36&amp;w=252&amp;s=2d678dc0fb3caf59015a1fe622b5207f</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>90d76f282f4b1f22</t>
+          <t>939c96e69ac99c8a</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2519,7 +2517,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>3 stk. pr.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2529,41 +2531,41 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Spangsberg is</t>
+          <t>Irma blåbær</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spangsberg</t>
+          <t>Irma</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>. 360-450 ml</t>
+          <t>. 200 g</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>80,56. kr/l</t>
+          <t>160,00. kr/kg</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1034803</t>
+          <t>1048626</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe347bd087aa51590bc7e4b878a42a6fe&amp;w=552&amp;s=5543c91b3a75ef7b5845e510c453aed5</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F49f214345531ed36643e7b3bdf4522c5&amp;w=385&amp;s=59c59635ab89a5922ba0046cae6214cf</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>c76c39cb3c98e131</t>
+          <t>d7180a3fd0e3423f</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2581,41 +2583,41 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Starbucks proteiniskaffe*</t>
+          <t>Cheasy eller Klovborg skæreost</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Cheasy</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>330 ml</t>
+          <t>. 495 g</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>45,45. kr/l</t>
+          <t>90,91. kr/kg</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1034807</t>
+          <t>1034788</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fed84c2cc76603758507bd8d990f63cca%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd4716187af4a7d41a7c912604bde9fe2&amp;w=552&amp;s=8fedbcf570337ca91ff3a8aa5ff6a153</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc4f9d928afded15b19cde18e81a0014d&amp;w=240&amp;s=f3bb46cb506ea6b43e0acab30ad329ee</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>a25555714d0e7aba</t>
+          <t>cd133a0b32cde4cd</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2633,17 +2635,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pandekager med hytteost*</t>
+          <t>Thise økologisk smør eller smørbart</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pandekager</t>
+          <t>Thise</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>200-240 g</t>
+          <t>200 g</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2657,17 +2659,17 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1034805</t>
+          <t>1048627</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F058c1339aa5e59b7dde5a19d50578970%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8d9f3caf6d26a3f0d66593621bc543b2&amp;w=252&amp;s=b30ea1c6aa2ca9cb1d9530501e5cfffe</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7dee88297891c169b7e25b83e03b7669&amp;w=552&amp;s=5d4f034c2480f894bad87e97114ab0d4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>d8e70d9977361216</t>
+          <t>94e22e2cd3c3393e</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2685,41 +2687,41 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LinusPro Whey100 proteinpulver*</t>
+          <t>Aalbæk spegepølse i skiver</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LinusPro</t>
+          <t>Aalbæk</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>60 g</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>222,50. kr/kg</t>
+          <t>266,67. kr/kg</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1048629</t>
+          <t>1034791</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7c9e2b776407a5350b9ea4160d71adcc%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F409ee3743ca8ffcac5890176d6712504%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd362c960c4e339ec00c8a1aa16b73dbb&amp;w=252&amp;s=699a236247c2e4101cdca1e637b114e7</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa349eb2605ee926eeefcda315387cf5b&amp;w=252&amp;s=b78352d25f74c098091b5ee6ff97c3eb</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>b5b31a484c5de5aa</t>
+          <t>db0c64323aca6be3</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2737,41 +2739,41 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Thise økologisk græsk inspireret yoghurt</t>
+          <t>Kohberg hvedebrød</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thise</t>
+          <t>Kohberg</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1 kg</t>
+          <t>. 380-500 g</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>28,00. kr/kg</t>
+          <t>47,37. kr/kg</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1034814</t>
+          <t>1034792</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7d284ea778cc1b0ccdc74263379c75c2&amp;w=552&amp;s=2c5fb43d317a52fda5a4a926101b9dd5</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F61f165afb25f96bca795b4eb565a21b5%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F59b6625d45ec457bbe40c16fbd1e1515%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F16b7c76c88204a13873a2802b58451bf&amp;w=252&amp;s=3e8269d2fd3b5389bccf12aec636a625</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>cf993c1983c7c919</t>
+          <t>95701aaf7f8a2c1c</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2789,41 +2791,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Thise økologisk skiveost</t>
+          <t>Tulip bacon 3-pak</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thise</t>
+          <t>Tulip</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>. 180-200 g</t>
+          <t>3 x 125 g</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>144,44. kr/kg</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>26</v>
-      </c>
+          <t>93,20. kr/kg</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1034810</t>
+          <t>1034793</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F680edf422655ac074e41e8612c3d2007&amp;w=552&amp;s=7fb3269a6ec06432dad5612284245ca3</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F75b95e65a141d19fcdc8214b35ce1c38&amp;w=252&amp;s=070824199a471d1ebe080f8bd9f19148</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>d7620cb431772ab3</t>
+          <t>a76658991962b69d</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2841,41 +2841,41 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Thise økologisk skæreost</t>
+          <t>Stryhns leverpostej*</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thise</t>
+          <t>Stryhns</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>. 432 g</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>113,43. kr/kg</t>
+          <t>50,00. kr/kg</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1034815</t>
+          <t>1034790</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fecbeed87751716d17eeb7ba2d1fc8672&amp;w=252&amp;s=a194f2d3177aaffb917245f7ac4a287c</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff8c35430559f4260c1952eb74aa237dd%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fcbe2e3d822215ecfd7e82285a8bec5d6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F494b93f91e0066315bf3e863ea7cc049&amp;w=252&amp;s=3cf177ac48dd630654fe2cf99013401e</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>d7e32a952d1d6a0a</t>
+          <t>d1f7d58a207aeaa0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2893,39 +2893,41 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Thise økologisk piskefløde</t>
+          <t>Havets fiskefrikadeller 2-pak</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Thise</t>
+          <t>Havets</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>500 ml</t>
+          <t>2 x 65 g</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>49,90. kr/l</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+          <t>76,92. kr/kg</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>10</v>
+      </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1034813</t>
+          <t>1034796</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9b88129794dd7576d563514d518de0e9&amp;w=252&amp;s=9280f36c4a468a8ae3568e228564169e</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F11fd40e808913426e746aa9eee93e587&amp;w=552&amp;s=7e0c428fa92338c4c12e0790b535b27b</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>c3c492c79b74c9c9</t>
+          <t>95b12b4ac4b58bda</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2943,41 +2945,41 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Thise økologisk jerseymælk*</t>
+          <t>Amanda gulfinnet tun*</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thise</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1 l</t>
+          <t>105 g</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>15,00. kr/l</t>
+          <t>114,29. kr/kg</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1034811</t>
+          <t>1034795</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6a3a11cd7f93e9580ce12c4e1fda0e5d&amp;w=252&amp;s=1144978883651ed928741974483c6665</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F42d8e8d3f06ef567b299df8126a250be%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa81e23b12d6f78c8737bafbcf8b3818c&amp;w=552&amp;s=d37e89718f195457a143be1e9a0cf206</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>d04a4ab54a7b69b6</t>
+          <t>80975739627e7938</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2995,41 +2997,41 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Änglamark økologisk sodavand</t>
+          <t>Royal Greenland Diskobay kutterrejer</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Royal</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1 l</t>
+          <t>230 g</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>12,00 kr/l</t>
+          <t>195,65. kr/kg</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1034816</t>
+          <t>1048628</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3d2fa2aca69e3cb7aeade1d88fe01898&amp;w=552&amp;s=96f1d2aca110ee957c2518dd3ed2cb78</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdf0ab0b622487d13c15db283840ad55c&amp;w=252&amp;s=711016fd5698a5c51367fbcc65279e65</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>91506cea2f936c9b</t>
+          <t>c14c16971e7b6b4c</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3047,41 +3049,41 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ânglamark økologisk knækbrød*</t>
+          <t>Glyngøre kullerfilet</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ânglamark</t>
+          <t>Glyngøre</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>. 180 g</t>
+          <t>225 g</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>111,11. kr/kg</t>
+          <t>173,33. kr/kg</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1034820</t>
+          <t>1034798</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6b0fb003e336bdbf9aab474d475fb487%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbdf142fcf89f5ae9a90231f8fab14b4c&amp;w=252&amp;s=00236f5b29a7d296c260c227a6c6b978</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0ec9d9a900838a72df69ef6eacfea760&amp;w=252&amp;s=afc7d443861039b8f6640b762f496b11</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>9333968cc5d06b7c</t>
+          <t>c41f2ee43113973b</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3099,39 +3101,41 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Änglamark økologiske havregryn</t>
+          <t>Glyngøre lakseportioner</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Glyngøre</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1000 g</t>
+          <t>225 g</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>11,95. kr/kg</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
+          <t>191,11. kr/kg</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>43</v>
+      </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1034794</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F576ace495cace5a0a20dbca35dfd0c92&amp;w=252&amp;s=d15a910c8db9987611aba52e37d66da8</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa0c58b46fbce52b47359e1e0d7f8be5e&amp;w=418&amp;s=439e14f261c6dc86b22928fad4d81ad1</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>953c6bc3c3c2d692</t>
+          <t>c03b6cdf103bd4cc</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3149,41 +3153,41 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Änglamark økologisk pizza</t>
+          <t>Polar is</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Polar</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>. 370-430 g</t>
+          <t>. 1 l</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>75,68. kr/kg</t>
+          <t>20,00. kr/kg</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1034818</t>
+          <t>1034804</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9f8d275df7180beefa5f87fe9575082a%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F47f95645094e8d71e9519592f89dfa13&amp;w=1152&amp;s=9ee61806c303d9d6fd62db3df77085db</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fee3917f0d07d64d3df9dab6f111f80c7%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdb54330ce073edcacd43d64a718ed9dd&amp;w=552&amp;s=4db1fabe17ba954a9d79d23b6d198d18</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>cbce34349bc63c38</t>
+          <t>90d76f282f4b1f22</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3201,37 +3205,41 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pizzaskærebræt inkl. pizzahjul*</t>
+          <t>Spangsberg is</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pizzaskærebræt</t>
+          <t>Spangsberg</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>. 1 stk</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>. 360-450 ml</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>80,56. kr/l</t>
+        </is>
+      </c>
       <c r="F54" t="n">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1034823</t>
+          <t>1034803</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb48c952ba86c340cdf7c051074c4b4c3&amp;w=552&amp;s=3693066abf5da156745f17be017c74bb</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe347bd087aa51590bc7e4b878a42a6fe&amp;w=552&amp;s=5543c91b3a75ef7b5845e510c453aed5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>85607ae178363d3e</t>
+          <t>c76c39cb3c98e131</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3249,7 +3257,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Coop surdejspizzabund*</t>
+          <t>Coop croissanter eller Irma pitabrød</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3259,31 +3267,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>240 g</t>
+          <t>. 330-440 g</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>62,50. kr/kg</t>
+          <t>54,55. kr/kg</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1034822</t>
+          <t>1034802</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F75347f71d12ba22f2430a3cc41f24182&amp;w=262&amp;s=049804e892ce7214e7338215d4459418</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F36d6692827ce3c761156a7bdf0743d86&amp;w=252&amp;s=52be33853c5ae666445ab98585ef732a</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>e1b9c6d6394c2372</t>
+          <t>b6310b2b50ce78cf</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3301,41 +3309,41 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Steff Houlberg topping</t>
+          <t>Rahbek fish &amp; chips eller lakselasagne</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Steff</t>
+          <t>Rahbek</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>175-200 g</t>
+          <t>. 350-400 g</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>91,43. kr/kg</t>
+          <t>82,86. kr/kg</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1034825</t>
+          <t>1034799</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F54a73479af8901f1c32574efc00896ad%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa7ade91c63ad2a682e500b14a15f0681&amp;w=252&amp;s=9ba763d0c770dad600e0a35a225f034f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2da7d2ae5ebf9cc6d03916c54cb0a047&amp;w=252&amp;s=1da10641ce7e8345dfeca604855eda37</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>ee6d11e23782669a</t>
+          <t>cc6d1eb3628cccf0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3353,41 +3361,41 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nye kartofler</t>
+          <t>Coop pølsehorn, focaccia med pepperoni eller Taquios</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Nye</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>. 1 kg</t>
+          <t>. 240-480 g</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>14,00. kr/kg</t>
+          <t>91,67. kr/kg</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1034824</t>
+          <t>1034801</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1723303248204d6c0d7b96240c69f40b&amp;w=252&amp;s=a38ff7878a1b6dcacad83bf76264841e</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fee333e70348119aec1d471238bcbd859&amp;w=333&amp;s=0fef3dbc875300a8a15f6445f515bc94</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>9ac771dc4e384c27</t>
+          <t>c3025af47db1658e</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3405,39 +3413,41 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Italiensk pålæg*</t>
+          <t>Starbucks proteiniskaffe*</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italiensk</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>70-125 g</t>
+          <t>330 ml</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>257,14. kr/kg</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
+          <t>45,45. kr/l</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>15</v>
+      </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1054381</t>
+          <t>1034807</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F82d714e58b04907eabab83a3b82e9798&amp;w=351&amp;s=92a6d10695cad901fe0261112fa6ca93</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fed84c2cc76603758507bd8d990f63cca%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd4716187af4a7d41a7c912604bde9fe2&amp;w=552&amp;s=8fedbcf570337ca91ff3a8aa5ff6a153</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>c0ba0096d734db3f</t>
+          <t>a25555714d0e7aba</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3455,41 +3465,41 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Urtekram økologisk olivenolie*</t>
+          <t>Barebells proteinbar eller proteindrik*</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Urtekram</t>
+          <t>Barebells</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1000 ml</t>
+          <t>55-56 g</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>99,00. kr/l</t>
+          <t>309,09 kr/kg</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1034827</t>
+          <t>1034808</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5bc097eba2f146c76f4cfc3f2c23af46&amp;w=252&amp;s=7f9bf8cf06382684b765a83d6fc67b71</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe57674a539bae599d95dfa4a32c829b4&amp;w=552&amp;s=c14a1eab85a5c766131b7f194550e773</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>d22d6d8465967993</t>
+          <t>c699639a71b61cc6</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3507,41 +3517,41 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Coop Grana padano</t>
+          <t>LinusPro Whey100 proteinpulver*</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>LinusPro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>150 g</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>166,67. kr/kg</t>
+          <t>222,50. kr/kg</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1034830</t>
+          <t>1048629</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb410282de7d835fc3d1246d912a1fdc3&amp;w=252&amp;s=32f32f0ad2cc214f9bc1c4cf98c82b98</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7c9e2b776407a5350b9ea4160d71adcc%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F409ee3743ca8ffcac5890176d6712504%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd362c960c4e339ec00c8a1aa16b73dbb&amp;w=252&amp;s=699a236247c2e4101cdca1e637b114e7</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>855e6ae165b6742a</t>
+          <t>b5b31a484c5de5aa</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3559,41 +3569,41 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Coop intenso tomater</t>
+          <t>Arla proteindrik, -mousse eller -pudding*</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Arla</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>. 200 g</t>
+          <t>200-500 g</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>100,00. kr/kg</t>
+          <t>60,00. kr/kg</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1034829</t>
+          <t>1034806</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F12786e818c2859e46d258899a713e352&amp;w=252&amp;s=bde4fee7f98e4f4d0d0dbfbfee9d8a16</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F909126c7c0e9c939d3d3f582351a8de4&amp;w=444&amp;s=e7c746c46ff5bcc59b423c26abefe1cf</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>87cd9293936396cc</t>
+          <t>d4f4d3bda2c91c14</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3611,41 +3621,41 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rummo Pasta*</t>
+          <t>Thise økologisk græsk inspireret yoghurt</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rummo</t>
+          <t>Thise</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>500 g</t>
+          <t>1 kg</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>36,00. kr/kg</t>
+          <t>28,00. kr/kg</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1034826</t>
+          <t>1034814</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7afbf74825775fca490ddda832d91afe&amp;w=252&amp;s=5a2b5498205bb8c9f8a85c41dbaa3927</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7d284ea778cc1b0ccdc74263379c75c2&amp;w=552&amp;s=2c5fb43d317a52fda5a4a926101b9dd5</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>c69b64663965399a</t>
+          <t>cf993c1983c7c919</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3663,41 +3673,41 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Brema fyldt pasta*</t>
+          <t>Thise økologisk skiveost</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brema</t>
+          <t>Thise</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>250-500 g</t>
+          <t>. 180-200 g</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>64,00. kr/kg</t>
+          <t>144,44. kr/kg</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1034831</t>
+          <t>1034810</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faa27f6f49403cbd9cf803fc8f9a7d7ce%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe7b88c083b9f2d956453d52a6ea48113%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8c7ee92dc49a87e482496b7372df707b&amp;w=252&amp;s=014c108e471ec6566c037c850770c709</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F680edf422655ac074e41e8612c3d2007&amp;w=552&amp;s=7fb3269a6ec06432dad5612284245ca3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>8bba5ef1308e290f</t>
+          <t>d7620cb431772ab3</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3715,41 +3725,41 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mutti tomatkonserves*</t>
+          <t>Thise økologisk vesterhavs- eller midsommerost*</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mutti</t>
+          <t>Thise</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>. 400 g</t>
+          <t>. 225 g</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>25,00. kr/kg</t>
+          <t>200,00. kr/kg</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1034828</t>
+          <t>1034812</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2e7bb17feba573081ac3019ad090581d%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6b8cf7e4abf881820d95fee88139b225%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4529591c8fed0461cdad88f39f8271f4&amp;w=252&amp;s=b086d8ce8111c6b30d25f2a72ea3974f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3786bd905846a77d13a59ad8e789500c&amp;w=252&amp;s=5a7d00113db7e09bf2ef5e7cee30ba63</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>eef21217790d0d4b</t>
+          <t>d5ef22d02d152d36</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3767,41 +3777,41 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Corny Big*</t>
+          <t>Thise økologisk skæreost</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Corny</t>
+          <t>Thise</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>. 40-50 g</t>
+          <t>. 432 g</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>150,00. kr/kg</t>
+          <t>113,43. kr/kg</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1034833</t>
+          <t>1034815</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F49b605786d73ca2384decbfa6ee97c89&amp;w=552&amp;s=fc703b53b677aa910d3c82c9a20ddd57</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fecbeed87751716d17eeb7ba2d1fc8672&amp;w=252&amp;s=a194f2d3177aaffb917245f7ac4a287c</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>c0e969d665e43c69</t>
+          <t>d7e32a952d1d6a0a</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3819,41 +3829,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Skælskør marmelade*</t>
+          <t>Thise økologisk piskefløde</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Skælskør</t>
+          <t>Thise</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>. 265 g</t>
+          <t>500 ml</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>56,60. kr/kg</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>15</v>
-      </c>
+          <t>49,90. kr/l</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1034835</t>
+          <t>1034813</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6bcf2c74f9b8d532329896e8d7d285ce%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa36ac2f5cae03123d1a78c05113a48ac%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F331c724fd819a2b41487c6a5dde92d25%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffa40fbf66655ffc0e5e9ab6054ae015b&amp;w=252&amp;s=2488c301f4ba3a0240ff9d073703f40f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9b88129794dd7576d563514d518de0e9&amp;w=252&amp;s=9280f36c4a468a8ae3568e228564169e</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>c5d032d0784f2fa7</t>
+          <t>c3c492c79b74c9c9</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3871,41 +3879,41 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Carletti chokopålæg</t>
+          <t>Thise økologisk jerseymælk*</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Carletti</t>
+          <t>Thise</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>221 g</t>
+          <t>1 l</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>135,75. kr/kg</t>
+          <t>15,00. kr/l</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1034834</t>
+          <t>1034811</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa90c2c4a287eb30e0db1f423a1397cb0%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffb4a50d859a405bb308fd5922a1221da&amp;w=252&amp;s=2e9177bf4291b26649c881911d6ad646</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6a3a11cd7f93e9580ce12c4e1fda0e5d&amp;w=252&amp;s=1144978883651ed928741974483c6665</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>d1c26ee06ee86e85</t>
+          <t>d04a4ab54a7b69b6</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -3923,22 +3931,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Valsemøllen mel*</t>
+          <t>Änglamark økologisk sodavand</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Valsemøllen</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1700-2000 g</t>
+          <t>1 l</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>7,06. kr/kg</t>
+          <t>12,00 kr/l</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -3947,17 +3955,17 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1034886</t>
+          <t>1034816</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F45245aa7cafc6008d35cd56b1f571c2e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F26c3bce03269f1b790b95f2e2dded4e6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F94f8684603f324e946da60c1ac847f45&amp;w=552&amp;s=ce5d4fc0d82ef650c4c876696d0be2f1</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3d2fa2aca69e3cb7aeade1d88fe01898&amp;w=552&amp;s=96f1d2aca110ee957c2518dd3ed2cb78</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>9189658c638e673f</t>
+          <t>91506cea2f936c9b</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -3975,41 +3983,41 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Santa Maria Smart Buy krydderier*</t>
+          <t>Änglamark økologiske kartofler eller brød</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Santa</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>. 30-400 g</t>
+          <t>. 420-500 g</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1,333,33. kr/kg</t>
+          <t>30,00. kr/kg</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1034885</t>
+          <t>1034817</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F03467c1ed0c0afd610cde63359f2dea8&amp;w=552&amp;s=c5bd45ed9b64bb704661cfe22eb7fd50</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F33af815ec265328d6eb9b0dd17c83a14&amp;w=552&amp;s=b58a312d60596a683f5a9a4fa47cc208</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>c43aa45b3b3ec12b</t>
+          <t>939230399a36cdcf</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4027,41 +4035,41 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Peanutbutter*</t>
+          <t>Ânglamark økologisk knækbrød*</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Peanutbutter*</t>
+          <t>Ânglamark</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1000 g</t>
+          <t>. 180 g</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>60,00. kr/kg</t>
+          <t>111,11. kr/kg</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1034884</t>
+          <t>1034820</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8cc00f414ae3aa3061232e5ee2b720b4&amp;w=252&amp;s=22cc0e8566bc7fd6f2d36a88329f4d36</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6b0fb003e336bdbf9aab474d475fb487%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbdf142fcf89f5ae9a90231f8fab14b4c&amp;w=252&amp;s=00236f5b29a7d296c260c227a6c6b978</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>c47b7b0432fbc8c1</t>
+          <t>9333968cc5d06b7c</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4079,41 +4087,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Kikkoman soyasauce*</t>
+          <t>Änglamark økologiske havregryn</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kikkoman</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>975-1000 ml</t>
+          <t>1000 g</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>61,54. kr/l</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>60</v>
-      </c>
+          <t>11,95. kr/kg</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1034887</t>
+          <t>1034819</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fde7cecaab8aff4d3930ec5bcd171b674&amp;w=252&amp;s=017aa70732ebf8ca219a7818c9dd6c4f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F576ace495cace5a0a20dbca35dfd0c92&amp;w=252&amp;s=d15a910c8db9987611aba52e37d66da8</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>b4e43b3b60859d0f</t>
+          <t>953c6bc3c3c2d692</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4131,41 +4137,41 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>YUM YUM nudler*</t>
+          <t>Änglamark økologisk pizza</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>360 g</t>
+          <t>. 370-430 g</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>88,89. kr/kg</t>
+          <t>75,68. kr/kg</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1034888</t>
+          <t>1034818</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F74588952e6845016a5d0d5fe75ae0437%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4a42498834202d43130d96a40f78cd57%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffa4e9e2ebeec5683d7b1605741de1182&amp;w=252&amp;s=4cf3342b6e80af049e8856fb295ce3ce</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9f8d275df7180beefa5f87fe9575082a%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F47f95645094e8d71e9519592f89dfa13&amp;w=1152&amp;s=9ee61806c303d9d6fd62db3df77085db</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>d678529325dbc493</t>
+          <t>cbce34349bc63c38</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4183,41 +4189,37 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bonduelle majs</t>
+          <t>Pizzaskærebræt inkl. pizzahjul*</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bonduelle</t>
+          <t>Pizzaskærebræt</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>420 g</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>42,86. kr/kg</t>
-        </is>
-      </c>
+          <t>. 1 stk</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1034889</t>
+          <t>1034823</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faf60b50696cae2a00ac66f9dcfaa5cd1&amp;w=252&amp;s=d782eff381e7f6fbd37ab41ffeb7e0a4</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb48c952ba86c340cdf7c051074c4b4c3&amp;w=552&amp;s=3693066abf5da156745f17be017c74bb</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>cbe83415d3eac8c5</t>
+          <t>85607ae178363d3e</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4235,41 +4237,41 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Katjes slikpose*</t>
+          <t>Coop surdejspizzabund*</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Katjes</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>250 g</t>
+          <t>240 g</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>120,00. kr/kg</t>
+          <t>62,50. kr/kg</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1034838</t>
+          <t>1034822</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F62fbf266b75af0d9b4d396a5d84457e9%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5d577196cb739f1ef5e3447997e4f751%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F483932ede27072eb11d19a11ab0cc3be&amp;w=552&amp;s=dd3845284042013e3b023c75b0bbc022</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F75347f71d12ba22f2430a3cc41f24182&amp;w=262&amp;s=049804e892ce7214e7338215d4459418</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>c2f13a0ae8fd86e2</t>
+          <t>e1b9c6d6394c2372</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4287,41 +4289,41 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Selection gaveæske</t>
+          <t>Coop ricotta eller formaggio revet ost*</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Selection</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>175 g</t>
+          <t>100-250 g</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>228,57. kr/kg</t>
+          <t>120,00. kr/kg</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1034839</t>
+          <t>1053744</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa5fecb08fde0f18f7c261423c0d2f2c0&amp;w=252&amp;s=e95e7065facc5bc13d1c00cfcc7b100c</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9833910f2d19be6da265b7b9379af8a3&amp;w=252&amp;s=e969cf66bd131a281af44296d15fb93e</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>c43b3bc444bb3bc4</t>
+          <t>c36d98c749366d86</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4339,41 +4341,41 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Samba 6-pak flødeboller*</t>
+          <t>Coop mascarpone, burrata eller maxi mozzarella*</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Samba</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>80 g</t>
+          <t>125-250 g</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>125,00. kr/kg</t>
+          <t>152,00. kr/kg</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1034891</t>
+          <t>1034821</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F451c3163f12716bd36f6c11bb447fd67%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff1ccd661a460a20f418b322547f40824&amp;w=552&amp;s=e190395991af98bbe740f3d5a1a4dce5</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1528f46056aae288350f750984426e0f&amp;w=252&amp;s=e5165517c8e2aaf17439515da1dc7b12</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>913997968669c7c3</t>
+          <t>950b6afc9f62a099</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4391,41 +4393,41 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Änglamark økologisk chokolade</t>
+          <t>Steff Houlberg topping</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Steff</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>. 100 g</t>
+          <t>175-200 g</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>250,00. kr/kg</t>
+          <t>91,43. kr/kg</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>1048631</t>
+          <t>1034825</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F87c7f4d3534932308db9391aeab5bc50&amp;w=552&amp;s=814552a939de0878d027c97ce114af96</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F54a73479af8901f1c32574efc00896ad%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa7ade91c63ad2a682e500b14a15f0681&amp;w=252&amp;s=9ba763d0c770dad600e0a35a225f034f</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>c4736e713cd08dc3</t>
+          <t>ee6d11e23782669a</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4443,41 +4445,41 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Skittles*</t>
+          <t>Nye kartofler</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Skittles*</t>
+          <t>Nye</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>152 g</t>
+          <t>. 1 kg</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>131,58. kr/kg</t>
+          <t>14,00. kr/kg</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1034890</t>
+          <t>1034824</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4d4f6379ac856fb09649c608eef9d6ef%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1853ef08e8f9aa360bb1dcd24407babd%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd536f69699e3deecc5f746bab0a33c66&amp;w=252&amp;s=5baa6943188aeb69c03c17bb8dd9442d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1723303248204d6c0d7b96240c69f40b&amp;w=252&amp;s=a38ff7878a1b6dcacad83bf76264841e</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>a6b65f19294d7074</t>
+          <t>9ac771dc4e384c27</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4495,41 +4497,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Karen Volf Kammerjunkere*</t>
+          <t>Italiensk pålæg*</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Italiensk</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>250-300 g</t>
+          <t>70-125 g</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>60,00. kr/kg</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>15</v>
-      </c>
+          <t>257,14. kr/kg</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1034893</t>
+          <t>1054381</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F007545cdd92b0d3dc460b09047240c63%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F949cfdae09037f0d90083a2b8a766859%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F33b245f15dcd39f161a971137fb2e6e4%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F56628fd293c2318cab492a2d44f2fa9e&amp;w=252&amp;s=09d8c93753ba672c22818112cbf00a65</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F82d714e58b04907eabab83a3b82e9798&amp;w=351&amp;s=92a6d10695cad901fe0261112fa6ca93</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>d5da1a487e052d2f</t>
+          <t>c0ba0096d734db3f</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Coop Corn Puffies</t>
+          <t>Urtekram økologisk olivenolie*</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Urtekram</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>80 g</t>
+          <t>1000 ml</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>175,00. kr/kg</t>
+          <t>99,00. kr/l</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1034892</t>
+          <t>1034827</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0a4f6cde8b551486d622d8b046cadc20&amp;w=252&amp;s=0a1d68dbdfbaed6ea8f6b2f00c6c4d63</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5bc097eba2f146c76f4cfc3f2c23af46&amp;w=252&amp;s=7f9bf8cf06382684b765a83d6fc67b71</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>94cb65789066639f</t>
+          <t>d22d6d8465967993</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4599,41 +4599,41 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Toffypops*</t>
+          <t>Coop Grana padano</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Toffypops*</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>120 g</t>
+          <t>150 g</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>83,33. kr/kg</t>
+          <t>166,67. kr/kg</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1034894</t>
+          <t>1034830</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb9ea36506018afe3db8353098cac2a36%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3c59e19b380b4cfd501692bb048de062&amp;w=252&amp;s=d0319b34299e0b5f814eb872bef7a519</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb410282de7d835fc3d1246d912a1fdc3&amp;w=252&amp;s=32f32f0ad2cc214f9bc1c4cf98c82b98</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>c0da3f25c5dac097</t>
+          <t>855e6ae165b6742a</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4651,41 +4651,41 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bavaria 6-pak</t>
+          <t>Coop intenso tomater</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bavaria</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>6 x 33 cl</t>
+          <t>. 200 g</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>12,63 kr/l</t>
+          <t>100,00. kr/kg</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1034847</t>
+          <t>1034829</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fff22e852d0ecaf5dc1b8ad08d560d242%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F919aee1e721d145c596bf110c6c44c7e&amp;w=552&amp;s=22b5565115c21e41d918a70039bc3b95</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F12786e818c2859e46d258899a713e352&amp;w=252&amp;s=bde4fee7f98e4f4d0d0dbfbfee9d8a16</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>ee671090611de6be</t>
+          <t>87cd9293936396cc</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4703,41 +4703,41 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ready To Drink</t>
+          <t>Rummo Pasta*</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ready</t>
+          <t>Rummo</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>25 cl</t>
+          <t>500 g</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>32,00 kr/l</t>
+          <t>36,00. kr/kg</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1048630</t>
+          <t>1034826</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5f1b91b6972dac153c02bd1a283c9757&amp;w=252&amp;s=8767b014c7922511ef8fa88a8db54f0e</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7afbf74825775fca490ddda832d91afe&amp;w=252&amp;s=5a2b5498205bb8c9f8a85c41dbaa3927</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>c23c2d1f3c2c3b93</t>
+          <t>c69b64663965399a</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -4755,41 +4755,41 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Harboe 2 liter</t>
+          <t>Brema fyldt pasta*</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Harboe</t>
+          <t>Brema</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>. 2 l</t>
+          <t>250-500 g</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>3,00 kr/l</t>
+          <t>64,00. kr/kg</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1034845</t>
+          <t>1034831</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F44c144a3fca9f85df8219558f1e36e8d&amp;w=252&amp;s=e7d641d86bb48369b980a004647b0a43</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faa27f6f49403cbd9cf803fc8f9a7d7ce%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe7b88c083b9f2d956453d52a6ea48113%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8c7ee92dc49a87e482496b7372df707b&amp;w=252&amp;s=014c108e471ec6566c037c850770c709</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>d9a7265626392ad9</t>
+          <t>8bba5ef1308e290f</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -4807,41 +4807,41 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Adobe Reserva</t>
+          <t>Mutti tomatkonserves*</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Mutti</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>. 75 cl</t>
+          <t>. 400 g</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>46,67. kr/l</t>
+          <t>25,00. kr/kg</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1034848</t>
+          <t>1034828</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9c2678478f66d11297b9b3ab99cc507e&amp;w=190&amp;s=28a9e394a0d42e993783ff6dab742f10</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2e7bb17feba573081ac3019ad090581d%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6b8cf7e4abf881820d95fee88139b225%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4529591c8fed0461cdad88f39f8271f4&amp;w=252&amp;s=b086d8ce8111c6b30d25f2a72ea3974f</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>b4e151f763a6260e</t>
+          <t>eef21217790d0d4b</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -4859,31 +4859,43 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DAY vinglas 4-pak*</t>
+          <t>Nestlé Cini minis eller Lion Minis morgenmad*</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DAY</t>
+          <t>Nestlé</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>51 cl</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>300 g</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>73,33. kr/kg</t>
+        </is>
+      </c>
       <c r="F86" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1034857</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
+          <t>1034836</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8fd501c788a602dbf45b1edf568f421b%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3f76ac4b2f4cf111c62dc993cef54c36&amp;w=552&amp;s=97ee8c92d36132a42088cd60ea42b97d</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>a84747f7018af639</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -4899,37 +4911,41 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Opbevaringsbøtter*</t>
+          <t>Corny Big*</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Opbevaringsbøtter*</t>
+          <t>Corny</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1,2 l</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
+          <t>. 40-50 g</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>150,00. kr/kg</t>
+        </is>
+      </c>
       <c r="F87" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1034858</t>
+          <t>1034833</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F35b1939fc2ecec23ff1a8ebf02f60968&amp;w=552&amp;s=cf6e072ce956c684357e82885b208e17</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F49b605786d73ca2384decbfa6ee97c89&amp;w=552&amp;s=fc703b53b677aa910d3c82c9a20ddd57</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>c16a37a548cb9d27</t>
+          <t>c0e969d665e43c69</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -4947,37 +4963,41 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Krydderiglas 12-pak*</t>
+          <t>Skælskør marmelade*</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Krydderiglas</t>
+          <t>Skælskør</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>12 stk</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
+          <t>. 265 g</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>56,60. kr/kg</t>
+        </is>
+      </c>
       <c r="F88" t="n">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1034855</t>
+          <t>1034835</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe06a384f29356285f0114995e1fca021&amp;w=252&amp;s=f9738c02d3539f7080e783fe2bc567e3</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6bcf2c74f9b8d532329896e8d7d285ce%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa36ac2f5cae03123d1a78c05113a48ac%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F331c724fd819a2b41487c6a5dde92d25%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffa40fbf66655ffc0e5e9ab6054ae015b&amp;w=252&amp;s=2488c301f4ba3a0240ff9d073703f40f</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>d5e92e0863952bb3</t>
+          <t>c5d032d0784f2fa7</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -4995,41 +5015,41 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Designservietter*</t>
+          <t>Carletti chokopålæg</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Designservietter*</t>
+          <t>Carletti</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>. 3-l</t>
+          <t>221 g</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0,50. kr/stk</t>
+          <t>135,75. kr/kg</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1034854</t>
+          <t>1034834</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1f13272fe981edb036e4b1f2aa31ce27&amp;w=252&amp;s=7a7e0625f4ba5a21ed978191a8f2ee3b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa90c2c4a287eb30e0db1f423a1397cb0%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffb4a50d859a405bb308fd5922a1221da&amp;w=252&amp;s=2e9177bf4291b26649c881911d6ad646</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>b5f74a080e6e91d5</t>
+          <t>d1c26ee06ee86e85</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5047,37 +5067,41 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Køkkenudstyr*</t>
+          <t>Gevalia eller Cafe Noir instant kaffe*</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Køkkenudstyr*</t>
+          <t>Gevalia</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>700 ml</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
+          <t>. 185-240 g</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>405,41. kr/kg</t>
+        </is>
+      </c>
       <c r="F90" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1034859</t>
+          <t>1034832</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbf9302d396aa888644019c8fcb511198&amp;w=252&amp;s=688908da2710145a5e24d7a441c03962</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F744bb305cc008b0a5bd3fbec999e5296&amp;w=448&amp;s=4e85ae293ab88ca0f821fb3bf32c39c5</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>cfce3130cdd93033</t>
+          <t>d2372de40fe20ab5</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5095,37 +5119,41 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Quiltet tæppe*</t>
+          <t>Valsemøllen mel*</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Quiltet</t>
+          <t>Valsemøllen</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>. 1 stk</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
+          <t>1700-2000 g</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>7,06. kr/kg</t>
+        </is>
+      </c>
       <c r="F91" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1034864</t>
+          <t>1034886</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F29cc953986ea2797fa6f8cbd5415b25c&amp;w=352&amp;s=f352071aa0695f772221f91b98854a11</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F45245aa7cafc6008d35cd56b1f571c2e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F26c3bce03269f1b790b95f2e2dded4e6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F94f8684603f324e946da60c1ac847f45&amp;w=552&amp;s=ce5d4fc0d82ef650c4c876696d0be2f1</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>d5d12afc4e902be8</t>
+          <t>9189658c638e673f</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5143,37 +5171,41 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Pude*</t>
+          <t>Santa Maria Smart Buy krydderier*</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pude*</t>
+          <t>Santa</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>. 1 stk</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
+          <t>. 30-400 g</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1,333,33. kr/kg</t>
+        </is>
+      </c>
       <c r="F92" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1034865</t>
+          <t>1034885</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb1c86eeeab3494dce4a4028c124bda9e&amp;w=352&amp;s=fc4a1e693690ec27631a80d216615eb2</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F03467c1ed0c0afd610cde63359f2dea8&amp;w=552&amp;s=c5bd45ed9b64bb704661cfe22eb7fd50</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>95f3680e6f0c2e39</t>
+          <t>c43aa45b3b3ec12b</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5191,37 +5223,41 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Dug*</t>
+          <t>Peanutbutter*</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dug*</t>
+          <t>Peanutbutter*</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>. 1 stk</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
+          <t>1000 g</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>60,00. kr/kg</t>
+        </is>
+      </c>
       <c r="F93" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1034866</t>
+          <t>1034884</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F52163bcdddda26c466610925a4ddae09&amp;w=352&amp;s=f972d72423cf7322833ebcf62f562adf</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8cc00f414ae3aa3061232e5ee2b720b4&amp;w=252&amp;s=22cc0e8566bc7fd6f2d36a88329f4d36</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>d56a3d35367a2425</t>
+          <t>c47b7b0432fbc8c1</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5239,31 +5275,43 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Nordicgrill engangsgrill*</t>
+          <t>Kikkoman soyasauce*</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Nordicgrill</t>
+          <t>Kikkoman</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
+          <t>975-1000 ml</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>61,54. kr/l</t>
+        </is>
+      </c>
       <c r="F94" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1034863</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+          <t>1034887</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fde7cecaab8aff4d3930ec5bcd171b674&amp;w=252&amp;s=017aa70732ebf8ca219a7818c9dd6c4f</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>b4e43b3b60859d0f</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -5279,37 +5327,41 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Sanex roll-on*</t>
+          <t>YUM YUM nudler*</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sanex</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>50 ml</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
+          <t>360 g</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>88,89. kr/kg</t>
+        </is>
+      </c>
       <c r="F95" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1034871</t>
+          <t>1034888</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fcead20adf02eac89758dc8b6977ce4fa%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8b0f1dbf7ae065c127528bc84bac7749%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5466b95be12ebef81b530342f60cab43&amp;w=552&amp;s=30b35184dc45355fcb178db5eaf193ac</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F74588952e6845016a5d0d5fe75ae0437%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4a42498834202d43130d96a40f78cd57%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffa4e9e2ebeec5683d7b1605741de1182&amp;w=252&amp;s=4cf3342b6e80af049e8856fb295ce3ce</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>c16b690b363e3665</t>
+          <t>d678529325dbc493</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5327,41 +5379,41 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Scholl fodpleje*</t>
+          <t>Bonduelle majs</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Scholl</t>
+          <t>Bonduelle</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>60 ml</t>
+          <t>420 g</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>650,00 kr/l</t>
+          <t>42,86. kr/kg</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1034868</t>
+          <t>1034889</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F22ebec14d3978e9a0c19f1063f57fabd&amp;w=252&amp;s=bac248120cd79c34d467cdbc25ed145b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faf60b50696cae2a00ac66f9dcfaa5cd1&amp;w=252&amp;s=d782eff381e7f6fbd37ab41ffeb7e0a4</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>83f4784b54094faf</t>
+          <t>cbe83415d3eac8c5</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5379,41 +5431,41 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>365 Minirisk personlig pleje</t>
+          <t>Katjes slikpose*</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>Katjes</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>. 50-200 ml</t>
+          <t>250 g</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>200,00. kr/l</t>
+          <t>120,00. kr/kg</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1034899</t>
+          <t>1034838</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F97acebc1be855f7fe9b54d30f69eb3e1&amp;w=252&amp;s=be1890c50cba1cf4ba48ccd7158c3cc8</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F62fbf266b75af0d9b4d396a5d84457e9%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5d577196cb739f1ef5e3447997e4f751%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F483932ede27072eb11d19a11ab0cc3be&amp;w=552&amp;s=dd3845284042013e3b023c75b0bbc022</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>94d33c958c1cdb3c</t>
+          <t>c2f13a0ae8fd86e2</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5431,41 +5483,41 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nutramino protein wafer*</t>
+          <t>Coop romkugler, træstammer eller mazarintærte</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Nutramino</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>35-39 g</t>
+          <t>200-275 g</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>285,71. kr/kg</t>
+          <t>60,00. kr/kg</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1034902</t>
+          <t>1034841</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faf1814139456acde7fa4d1bdcf713724%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F962c989315cb630c65684df586a6c841%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc24d95ea550341865becb38b1e78f222&amp;w=552&amp;s=a36dbc573f2e472b497f055cbe4ec528</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd0f1158a0b8faf7d2d0ccfa4afa8d072&amp;w=552&amp;s=39bc0c9217e891f6bff2f69324f95c04</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>dfb62009f8f0c665</t>
+          <t>c5b44b99784836cf</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5483,41 +5535,41 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Schulstad Signaturbrød</t>
+          <t>Tuc baked rolls eller trio 3-pak*</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Schulstad</t>
+          <t>Tuc</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>. 600-850 g</t>
+          <t>150-300 g</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>26,67. kr/kg</t>
+          <t>133,33. kr/kg</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1034873</t>
+          <t>1034837</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=612&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdb89ee4ccb039a305fb4773d5311a2ca&amp;w=552&amp;s=b8e48b5fa4d6c56bd660394e69864572</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F68968b6023e99304231487652268e65d%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1f93155e1a41c8e234a39bb1f5cfcd48%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F542a0c550ed3c12c4f82da823a261a53%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa070edaebfcf11267bc3b57acd6cabbe&amp;w=252&amp;s=3422a04b66d8b848fb2261ecd87c2ef9</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>cf9c3c6dc792902c</t>
+          <t>d37206857827a7f2</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5535,41 +5587,41 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Fjerkræs kyllingepålæg*</t>
+          <t>Selection gaveæske</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Fjerkræs</t>
+          <t>Selection</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>80 g</t>
+          <t>175 g</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>175,00. kr/kg</t>
+          <t>228,57. kr/kg</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1034874</t>
+          <t>1034839</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5719b5ea4bfac57e784e95159d60dce9&amp;w=552&amp;s=c461e15efa9448d72354e0b67cd77b84</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa5fecb08fde0f18f7c261423c0d2f2c0&amp;w=252&amp;s=e95e7065facc5bc13d1c00cfcc7b100c</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>9b26cc8ccccc6dcc</t>
+          <t>c43b3bc444bb3bc4</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -5587,41 +5639,41 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Innocent kids smoothies</t>
+          <t>Nestlé eller Mars barer*</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Innocent</t>
+          <t>Nestlé</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>4 x 150 ml</t>
+          <t>. 38-51 g</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>33,33. kr/l</t>
+          <t>263,16. kr/kg</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1034876</t>
+          <t>1034840</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7c24cf5901bfcdfc19847ff5fc2c1518&amp;w=252&amp;s=100ce1f7f7e33e303c31a9e6427df648</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6270740a4f3453808e5d93011a734e68&amp;w=1152&amp;s=1b81330da7dd92cedaf0897c2adc8018</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>85976c9f3cc81d8c</t>
+          <t>9bce313969926633</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -5639,41 +5691,41 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Stjernehaps*</t>
+          <t>Samba 6-pak flødeboller*</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Stjernehaps*</t>
+          <t>Samba</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>100 g</t>
+          <t>80 g</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>200,00. kr/kg</t>
+          <t>125,00. kr/kg</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1034875</t>
+          <t>1034891</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7731530d602b354fee7eec75418f6bdb&amp;w=252&amp;s=f042cbb0d14439a092535b2a805cf7fe</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F451c3163f12716bd36f6c11bb447fd67%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff1ccd661a460a20f418b322547f40824&amp;w=552&amp;s=e190395991af98bbe740f3d5a1a4dce5</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>92939e6a67662cc9</t>
+          <t>913997968669c7c3</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -5691,41 +5743,41 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Klovborg skiveost</t>
+          <t>Änglamark økologisk chokolade</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Klovborg</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>200-240 g</t>
+          <t>. 100 g</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>110,00. kr/kg</t>
+          <t>250,00. kr/kg</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>1034877</t>
+          <t>1048631</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faa4e03edf4be7c509942c6da61f29316&amp;w=315&amp;s=e0680be48c9625b52741ae3aa5bb9453</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F87c7f4d3534932308db9391aeab5bc50&amp;w=552&amp;s=814552a939de0878d027c97ce114af96</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>90585dd24f9e1e69</t>
+          <t>c4736e713cd08dc3</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -5743,41 +5795,41 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Irma pålægssalater*</t>
+          <t>Skittles*</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Skittles*</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>150-175 g</t>
+          <t>152 g</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>166,67. kr/kg</t>
+          <t>131,58. kr/kg</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1034955</t>
+          <t>1034890</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F91523bcb85ccdd30cd56e43b4ea830de&amp;w=552&amp;s=019a9893482ac2a0c2a16c29e3321ec4</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4d4f6379ac856fb09649c608eef9d6ef%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1853ef08e8f9aa360bb1dcd24407babd%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd536f69699e3deecc5f746bab0a33c66&amp;w=252&amp;s=5baa6943188aeb69c03c17bb8dd9442d</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>d097076a171b7a2d</t>
+          <t>a6b65f19294d7074</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -5795,41 +5847,41 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Irma rejer*</t>
+          <t>Karen Volf Kammerjunkere*</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>. 150 g</t>
+          <t>250-300 g</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>166,67. kr/kg</t>
+          <t>60,00. kr/kg</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1034958</t>
+          <t>1034893</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb0184c196a7eec7d75ad28f2d59e64e5&amp;w=236&amp;s=3bbb5bd38d993ce5b54d4d3820ec2646</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F007545cdd92b0d3dc460b09047240c63%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F949cfdae09037f0d90083a2b8a766859%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F33b245f15dcd39f161a971137fb2e6e4%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F56628fd293c2318cab492a2d44f2fa9e&amp;w=252&amp;s=09d8c93753ba672c22818112cbf00a65</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>c53d7ac1346a6a96</t>
+          <t>d5da1a487e052d2f</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -5847,33 +5899,41 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Irma karklude 2-pak*</t>
+          <t>Coop Corn Puffies</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Irma</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+          <t>Coop</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>80 g</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>175,00. kr/kg</t>
+        </is>
+      </c>
       <c r="F106" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>1034957</t>
+          <t>1034892</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5c7d946f1c43c1d8df40ae8670ea3b80&amp;w=476&amp;s=2af3292ace68679b45bd67e82dbe4e11</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0a4f6cde8b551486d622d8b046cadc20&amp;w=252&amp;s=0a1d68dbdfbaed6ea8f6b2f00c6c4d63</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>e4a41a5c4d1f4b3b</t>
+          <t>94cb65789066639f</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -5891,41 +5951,41 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Irma økologiske pølser*</t>
+          <t>Toffypops*</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Toffypops*</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>240-280 g</t>
+          <t>120 g</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>145,83. kr/kg</t>
+          <t>83,33. kr/kg</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>1034963</t>
+          <t>1034894</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F353894a931dc477df51e47b557306229&amp;w=552&amp;s=e8623e598f6dfa57686dd54811332e1f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb9ea36506018afe3db8353098cac2a36%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3c59e19b380b4cfd501692bb048de062&amp;w=252&amp;s=d0319b34299e0b5f814eb872bef7a519</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>8e1f71e21e9f8b08</t>
+          <t>c0da3f25c5dac097</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -5943,41 +6003,41 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Irma brioche fastfoodbrød</t>
+          <t>Faxe Kondi, Pepsi max, Heineken eller Royal øl</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Faxe</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>250-270 g</t>
+          <t>. 18-20 x 33 cl</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>88,00. kr/kg</t>
+          <t>13,30 kr/l</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1034961</t>
+          <t>1034842</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F894e784a8aa7168a2956c6d43566d966&amp;w=252&amp;s=8df21a4f731af7b85be48f16e2ed4d5c</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F196954ce52495d74237a04ef3152b797&amp;w=552&amp;s=071271e49deb5c9ee047bc3e5e6e6d9e</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>ba1845e7ee51a82e</t>
+          <t>9a93399cc363ce92</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -5995,41 +6055,41 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Irma oliven*</t>
+          <t>Bavaria 6-pak</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>70 g</t>
+          <t>6 x 33 cl</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>142,86. kr/kg</t>
+          <t>12,63 kr/l</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1034964</t>
+          <t>1034847</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe588e54bbc22f92805dfb99bfa572ffe&amp;w=552&amp;s=13d5f17f282449014739bcf9a7b2f679</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fff22e852d0ecaf5dc1b8ad08d560d242%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F919aee1e721d145c596bf110c6c44c7e&amp;w=552&amp;s=22b5565115c21e41d918a70039bc3b95</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>d1151fec6e6b2305</t>
+          <t>ee671090611de6be</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6047,41 +6107,41 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Irma danske lakseportioner</t>
+          <t>1664, Breezer, Smirnoff eller Somersby</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>1664,</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>. 200 g</t>
+          <t>. 27,5-33 cl</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>245,00. kr/kg</t>
+          <t>47,27 kr/l</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1034967</t>
+          <t>1034846</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F12538a579cd59f7bf75ef8c1cc10c294&amp;w=252&amp;s=68757a8eab939fd9bdf9317db70b73f7</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd4189d474763fe6a98816808f5b83f90&amp;w=252&amp;s=d71408e26e3e2bd968b0103134b976f6</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>a851779c5f2788d8</t>
+          <t>c4f12f1b2c9a3e2c</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6099,41 +6159,41 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Irma islandsk flagesalt*</t>
+          <t>Ready To Drink</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>250 g</t>
+          <t>25 cl</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>112,00. kr/kg</t>
+          <t>32,00 kr/l</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1034965</t>
+          <t>1048630</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6e564b25154bdfe1e2acc19d5f565276&amp;w=252&amp;s=6eccfc2752dbcf8377eb8797a08b24a9</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5f1b91b6972dac153c02bd1a283c9757&amp;w=252&amp;s=8767b014c7922511ef8fa88a8db54f0e</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>a5ca64cb37340b37</t>
+          <t>c23c2d1f3c2c3b93</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6151,41 +6211,41 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Irma økologisk pizza*</t>
+          <t>Fun eller Scoop læskedrik*</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Fun</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>. 400 g</t>
+          <t>. 50 cl</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>137,50. kr/kg</t>
+          <t>24,00. kr/l</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>1034968</t>
+          <t>1034843</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fac0ea3352a57bc3330dfcf0394155979&amp;w=494&amp;s=af997c36ae1b13af565b8d189269ee00</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F09895029801e2118da7dbd0dbb8e666c&amp;w=252&amp;s=c7eacac7e0a690fe26b990b0e18453f8</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>d3934c9159b033fc</t>
+          <t>cf39390b51ec30bc</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6203,41 +6263,41 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Irma frugttærte*</t>
+          <t>Harboe 2 liter</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Harboe</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>. 430 g</t>
+          <t>. 2 l</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>116,67. kr/kg</t>
+          <t>3,00 kr/l</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1034969</t>
+          <t>1034845</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fda36869ad20d4c012eb3e098e1cba101&amp;w=552&amp;s=e833fa48a74a558bb5e01adf92134368</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F44c144a3fca9f85df8219558f1e36e8d&amp;w=252&amp;s=e7d641d86bb48369b980a004647b0a43</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>95356ac8b52fd2d0</t>
+          <t>d9a7265626392ad9</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6255,41 +6315,41 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Irma marcipanbrød*</t>
+          <t>Adobe Reserva</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>35 g</t>
+          <t>. 75 cl</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>342,86. kr/kg</t>
+          <t>46,67. kr/l</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1034970</t>
+          <t>1034848</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F516aee6d859dccdeff91abcd2d2ea4ac&amp;w=552&amp;s=76a6844ca773a26d8251e6c0909a6710</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9c2678478f66d11297b9b3ab99cc507e&amp;w=190&amp;s=28a9e394a0d42e993783ff6dab742f10</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>cb9461d936c963cc</t>
+          <t>b4e151f763a6260e</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6307,49 +6367,1957 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Irma lakridskugler*</t>
+          <t>Giordano Organic eller Duc Royal Blanc de Blancs</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Giordano</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>110 g</t>
+          <t>. 75 cl</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>318,18. kr/kg</t>
+          <t>78,67. kr/l</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
+          <t>1034852</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff7b45cd9a92df90b427f6b64f8a86714&amp;w=247&amp;s=ea444e54845c0b7ccb1b83424d0ec3cf</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>b54530c8cbb74bb4</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>100% Grenache, 100% Chardonnay, Giordano Ricarico Prestige eller Mateus Rosé</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>. 75 cl</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>66,67. kr/l</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>50</v>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>1034853</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdb33ac3dc2670f2351168306f5d9377b&amp;w=252&amp;s=8feb6bb33a9052f85b9cefece96cf20b</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>a5157aa65afa3862</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>ISH, Monastere Abbey, Nørrebro Bryghus eller Sol*</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ISH,</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>. 33-50 cl</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>30,30 kr/l</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>10</v>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>1034850</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F47eea480f829fa09f30ced4af15e8d78&amp;w=252&amp;s=08cbaf79cad80a47814c960f384e1058</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>ba0f0df252f04d2d</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Anarkist, Humlesovs,!PA eller Willemoes øl*</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Anarkist,</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>. 44-50 cl</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>40,91 kr/l</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>18</v>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>1034851</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F23ad61366d5e2ac250f2a1e1377759c1&amp;w=252&amp;s=f8896cc40f521f45bb4da915b0b523f7</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>df2525a1dada2c64</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Baileys Likør, Smirnoff Vodka, Gammel Dansk Bitter, Captain Morgan eller Gordon's Gin</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Baileys</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>70 cl</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>155,71. kr/l</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>109</v>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>1034849</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F266b69e7b083c97f3dbc5bb22f766d95%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F836d84a93e9cc225b16e96023e832172%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa544e7c7ebf5cd80e51c35a437697374%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F132ee033f2502c34580638f066cfc253%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F18387b9bd2327d1570275880849b01f9&amp;w=252&amp;s=acba5a87bf8e0df95c40a471b97b524e</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>f669099e32d6286d</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>DAY vinglas 4-pak*</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>DAY</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>51 cl</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="n">
+        <v>49</v>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>1034857</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Krydderiglas 12-pak*</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Krydderiglas</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>12 stk</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="n">
+        <v>95</v>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>1034855</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe06a384f29356285f0114995e1fca021&amp;w=252&amp;s=f9738c02d3539f7080e783fe2bc567e3</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>d5e92e0863952bb3</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Designservietter*</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Designservietter*</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>. 3-l</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>0,50. kr/stk</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>10</v>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>1034854</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1f13272fe981edb036e4b1f2aa31ce27&amp;w=252&amp;s=7a7e0625f4ba5a21ed978191a8f2ee3b</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>b5f74a080e6e91d5</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Køkkenudstyr*</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Køkkenudstyr*</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>700 ml</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="n">
+        <v>89</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>1034859</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbf9302d396aa888644019c8fcb511198&amp;w=252&amp;s=688908da2710145a5e24d7a441c03962</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>cfce3130cdd93033</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Quiltet tæppe*</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Quiltet</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>. 1 stk</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="n">
+        <v>60</v>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>1034864</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F29cc953986ea2797fa6f8cbd5415b25c&amp;w=352&amp;s=f352071aa0695f772221f91b98854a11</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>d5d12afc4e902be8</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Pude*</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Pude*</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>. 1 stk</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="n">
+        <v>50</v>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>1034865</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb1c86eeeab3494dce4a4028c124bda9e&amp;w=352&amp;s=fc4a1e693690ec27631a80d216615eb2</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>95f3680e6f0c2e39</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Solcelle bord- eller væglampe med mønster*</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Solcelle</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>. 1 stk</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="n">
+        <v>30</v>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>1034862</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Nordicgrill engangsgrill*</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Nordicgrill</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="n">
+        <v>25</v>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>1034863</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Longo Vital eller Futura*</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Longo</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>150-180 stk</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>0,77. kr/stk</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>115</v>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>1034869</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa88d1f2153f85f04d87881f719969277&amp;w=252&amp;s=0c279a2c889c57a4a98768e61cec0bdb</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>f934504d265736da</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Best Friend snack eller Sheba fresh &amp; fine menuboks*</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Best</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>180-300 g</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>138,89. kr/kg</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>25</v>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>1034872</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0997db2b340e7879f09ce7500b789a73&amp;w=252&amp;s=7fcd14f93615ab9c8c116e3dc114d345</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>c50526fa785a1bda</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>365 Minirisk personlig pleje</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>. 50-200 ml</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>200,00. kr/l</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>10</v>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>1034899</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F97acebc1be855f7fe9b54d30f69eb3e1&amp;w=252&amp;s=be1890c50cba1cf4ba48ccd7158c3cc8</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>94d33c958c1cdb3c</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Nutramino protein wafer*</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Nutramino</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>35-39 g</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>285,71. kr/kg</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>10</v>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>1034902</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faf1814139456acde7fa4d1bdcf713724%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F962c989315cb630c65684df586a6c841%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc24d95ea550341865becb38b1e78f222&amp;w=552&amp;s=a36dbc573f2e472b497f055cbe4ec528</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>dfb62009f8f0c665</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Schulstad Signaturbrød</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Schulstad</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>. 600-850 g</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>26,67. kr/kg</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>16</v>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>1034873</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=612&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdb89ee4ccb039a305fb4773d5311a2ca&amp;w=552&amp;s=b8e48b5fa4d6c56bd660394e69864572</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>cf9c3c6dc792902c</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Fjerkræs kyllingepålæg*</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Fjerkræs</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>80 g</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>175,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>14</v>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>1034874</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5719b5ea4bfac57e784e95159d60dce9&amp;w=552&amp;s=c461e15efa9448d72354e0b67cd77b84</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>9b26cc8ccccc6dcc</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Innocent kids smoothies</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Innocent</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>4 x 150 ml</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>33,33. kr/l</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>20</v>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>1034876</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7c24cf5901bfcdfc19847ff5fc2c1518&amp;w=252&amp;s=100ce1f7f7e33e303c31a9e6427df648</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>85976c9f3cc81d8c</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Stjernehaps*</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Stjernehaps*</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>100 g</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>200,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>20</v>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>1034875</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7731530d602b354fee7eec75418f6bdb&amp;w=252&amp;s=f042cbb0d14439a092535b2a805cf7fe</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>92939e6a67662cc9</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Klovborg skiveost</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Klovborg</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>200-240 g</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>110,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>22</v>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>1034877</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faa4e03edf4be7c509942c6da61f29316&amp;w=315&amp;s=e0680be48c9625b52741ae3aa5bb9453</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>90585dd24f9e1e69</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Irma pålægssalater*</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>150-175 g</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>166,67. kr/kg</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>25</v>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>1034955</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F91523bcb85ccdd30cd56e43b4ea830de&amp;w=552&amp;s=019a9893482ac2a0c2a16c29e3321ec4</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>d097076a171b7a2d</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Irma rejer*</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>. 150 g</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>166,67. kr/kg</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>25</v>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>1034958</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb0184c196a7eec7d75ad28f2d59e64e5&amp;w=236&amp;s=3bbb5bd38d993ce5b54d4d3820ec2646</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>c53d7ac1346a6a96</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Irma røget- eller gravad laks*</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>125 g</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>280,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>35</v>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>1034959</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3ac76c65ec17f86ad69e568b09b74a39%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5072fabf0085c8d12e6f57614873ed21&amp;w=252&amp;s=95f1c1cf5036718c6b495da0b3c598fa</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>89473cbc462f1ab9</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Irma viskestykker 3-pak*</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="n">
+        <v>89</v>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>1034956</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F323d9c9002a9ed0dbcb2bd1a37bd10d1&amp;w=252&amp;s=72bee86cc9dcc478caa980330b6d43bd</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>d1392ac6a4b3b14f</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Irma karklude 2-pak*</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="n">
+        <v>49</v>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>1034957</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5c7d946f1c43c1d8df40ae8670ea3b80&amp;w=476&amp;s=2af3292ace68679b45bd67e82dbe4e11</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>e4a41a5c4d1f4b3b</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Irma økologiske pølser*</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>240-280 g</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>145,83. kr/kg</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>35</v>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>1034963</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F353894a931dc477df51e47b557306229&amp;w=552&amp;s=e8623e598f6dfa57686dd54811332e1f</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>8e1f71e21e9f8b08</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Irma ketchup eller sennep*</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>205-340 g</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>87,80. kr/kg</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>18</v>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>1034960</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3d73f1538f8ed1740d01e7a52bd7638e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7afab2b3f27e213ea82fa92e387436bc&amp;w=262&amp;s=813a7ee015fdd18163cd3468e7bacd61</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>856b6ae695e4626c</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Irma remoulade eller mayonnaise i pose*</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>200-250 g</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>75,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>15</v>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>1034962</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1cb3b1031bb0841a04127fafa7a5352c%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc1062414b8e576495db1b5caa30484f6&amp;w=252&amp;s=ce425beeb0294fdcbbd50fa48ff4c9f6</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>91e43d6a644b2c7e</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Irma brioche fastfoodbrød</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>250-270 g</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>88,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>22</v>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>1034961</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=241&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F894e784a8aa7168a2956c6d43566d966&amp;w=252&amp;s=8df21a4f731af7b85be48f16e2ed4d5c</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>ba1845e7ee51a82e</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Irma oliven*</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>70 g</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>142,86. kr/kg</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>10</v>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>1034964</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe588e54bbc22f92805dfb99bfa572ffe&amp;w=552&amp;s=13d5f17f282449014739bcf9a7b2f679</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>d1151fec6e6b2305</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Irma danske lakseportioner</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>. 200 g</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>245,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>49</v>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>1034967</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F12538a579cd59f7bf75ef8c1cc10c294&amp;w=252&amp;s=68757a8eab939fd9bdf9317db70b73f7</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>a851779c5f2788d8</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Irma islandsk flagesalt*</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>250 g</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>112,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>28</v>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>1034965</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6e564b25154bdfe1e2acc19d5f565276&amp;w=252&amp;s=6eccfc2752dbcf8377eb8797a08b24a9</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>a5ca64cb37340b37</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Irma økologisk pizza*</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>. 400 g</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>137,50. kr/kg</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>55</v>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>1034968</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fac0ea3352a57bc3330dfcf0394155979&amp;w=494&amp;s=af997c36ae1b13af565b8d189269ee00</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>d3934c9159b033fc</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Irma frugttærte*</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>. 430 g</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>116,67. kr/kg</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>49</v>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>1034969</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=631&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fda36869ad20d4c012eb3e098e1cba101&amp;w=552&amp;s=e833fa48a74a558bb5e01adf92134368</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>95356ac8b52fd2d0</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Irma marcipanbrød*</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>35 g</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>342,86. kr/kg</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>12</v>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>1034970</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F516aee6d859dccdeff91abcd2d2ea4ac&amp;w=552&amp;s=76a6844ca773a26d8251e6c0909a6710</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>cb9461d936c963cc</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Irma lakridskugler*</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>110 g</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>318,18. kr/kg</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>35</v>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
           <t>1034972</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="I152" t="inlineStr">
         <is>
           <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=260&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb57f778bb724441ef0985a38c33e254c&amp;w=252&amp;s=53dca89db47fa4709a0a14a3e58cf5eb</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
+      <c r="J152" t="inlineStr">
         <is>
           <t>c334343c3c37db38</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Irma formalet kaffe eller hele kaffebønner*</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>. 350-500 g</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>168,57. kr/kg</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>59</v>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>1034971</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=222&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F529b93bf2fc33433b7590d8d49c7d317&amp;w=252&amp;s=51aec314630f32ec49045e03c7b60ab6</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>95936e5c7368e183</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
